--- a/public/downloads/Auditor_Anomaly_Testing_Template.xlsx
+++ b/public/downloads/Auditor_Anomaly_Testing_Template.xlsx
@@ -5,38 +5,44 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sorat\Desktop\Coding\kitopi_trash\Auditor_Toolkit_Pack\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sorat\Desktop\Coding\portfolio_my\public\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB6D5E5-969A-488A-856B-BC3A06A77407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88176079-4FED-4E77-A6DB-250C3F92667A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="00_Field_Guide" sheetId="1" r:id="rId1"/>
-    <sheet name="01_Field_CheatSheet" sheetId="2" r:id="rId2"/>
+    <sheet name="00_Instructions" sheetId="1" r:id="rId1"/>
+    <sheet name="01_Triage_Rubric" sheetId="2" r:id="rId2"/>
     <sheet name="02_IT_Data_Request" sheetId="3" r:id="rId3"/>
     <sheet name="Test1_Split_POs" sheetId="4" r:id="rId4"/>
     <sheet name="Test2_Dormant_Vendors" sheetId="5" r:id="rId5"/>
     <sheet name="Test3_Duplicate_Invoices" sheetId="6" r:id="rId6"/>
     <sheet name="Test4_Off_Hours_GL" sheetId="7" r:id="rId7"/>
     <sheet name="Test5_Round_Sum_Services" sheetId="8" r:id="rId8"/>
-    <sheet name="99_Audit_Exceptions_Summary" sheetId="9" r:id="rId9"/>
+    <sheet name="99_Summary" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="508">
-  <si>
-    <t>CONTINUOUS CONTROLS MONITORING: FIELD OPERATING PROTOCOL</t>
-  </si>
-  <si>
-    <t>Deterministic Anomaly Testing &amp; Exposure Quantification across 100% Population Telemetry</t>
-  </si>
-  <si>
-    <t>Framework Architect: Majid Mumtaz | CIA, ACA (ICAEW), FCCA, GRCP, GRCA, COSO ERM</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="540">
+  <si>
+    <t>INTERNAL AUDIT CONTINUOUS CONTROL TESTING TEMPLATE</t>
+  </si>
+  <si>
+    <t>Automated Population Exception Testing: Procurement, Accounts Payable &amp; General Ledger</t>
+  </si>
+  <si>
+    <t>Framework Architect:</t>
+  </si>
+  <si>
+    <t>Majid Mumtaz | CIA, ACA (ICAEW), FCCA, GRCP, GRCA, COSO ERM</t>
+  </si>
+  <si>
+    <t>Author Profiles:</t>
   </si>
   <si>
     <t>Portfolio &amp; Tools</t>
@@ -45,63 +51,150 @@
     <t>LinkedIn Profile</t>
   </si>
   <si>
-    <t>1. OPERATIONAL REALITY VS. SAMPLE-BASED COMPLIANCE</t>
-  </si>
-  <si>
-    <t>Traditional audit methodology inspects 20 to 25 sampled vouchers to verify whether authorized signatures exist on paper forms. In operational reality, an authorized signature on an empty warehouse receipt or a partitioned invoice still represents EBITDA leakage. A 25-sample pull out of 50,000 transactions covers 0.05% of activity—statistically blind to intentional circumventions.</t>
-  </si>
-  <si>
-    <t>Operational breakdowns follow predictable structural patterns: purchase orders clustered just beneath Delegation of Authority (DOA) ceilings, payments routed through dormant vendor accounts with newly altered bank details, punctuation substitutions designed to evade ERP duplicate validations, and late-night manual journal entries entered under month-end close pressure.</t>
-  </si>
-  <si>
-    <t>This protocol replaces sample inspection with 100% population deterministic telemetry in standard Excel.</t>
-  </si>
-  <si>
-    <t>2. WORKBOOK ARCHITECTURE</t>
-  </si>
-  <si>
-    <t>• Tab '00_Field_Guide': Operating methodology, formula mechanics, and executive EBITDA framing standards.
-• Tab '01_Field_CheatSheet': 1-page rapid triage rubric, audit evidence requirements, and diagnostic interview dialogue.
-• Tab '02_IT_Data_Request': Standard service desk data extraction ticket for IT database administrators.
-• Tabs 'Test1_Split_POs' to 'Test5_Round_Sum_Services': Dynamic Excel Tables with native calculation logic.
-• Tab '99_Audit_Exceptions_Summary': Dynamic executive dashboard reporting population exception counts, rates, and quantified exposure.</t>
-  </si>
-  <si>
-    <t>3. FIELDWORK EXECUTION WORKFLOW</t>
-  </si>
-  <si>
-    <t>1. Data Acquisition: Transmit Tab '02_IT_Data_Request' to IT or Finance Systems. Require raw flat CSV exports.
-2. Ingestion: Navigate to the relevant testing sheet (e.g. 'Test1_Split_POs'). Paste raw data directly into the input columns (Columns A to H).
-3. Automatic Propagation: All calculation formulas reside inside dynamic Excel Tables and expand automatically to 100% of rows.
-4. Exception Triage: Filter the 'Audit_Flag' column for 'FLAG: ...'. Every flagged row is an exception requiring inquiry.
-5. Defensibility: Check Tab '99_Audit_Exceptions_Summary'. It aggregates exposures automatically using structured table references.
-6. Substantive Inquiry: Use the diagnostic interview questions in Tab '01_Field_CheatSheet' to assess whether exceptions represent deliberate circumvention or operational coping mechanisms.</t>
-  </si>
-  <si>
-    <t>4. THE 5 CORE TESTING MECHANISMS</t>
-  </si>
-  <si>
-    <t>• Test 1 (Split POs): Evaluates procurement commitments partitioned below $10,000 issued within 5 days to the same supplier by the same buyer (Sum &gt;= $10,000).
-• Test 2 (Dormant Vendors): Flags disbursements to suppliers inactive for &gt;180 days whose bank coordinates were modified &lt;= 30 days prior to payment.
-• Test 3 (Duplicate Invoices): Normalizes invoice strings (stripping spaces, hyphens, slashes, dots, underscores, hashes, colons) to identify double payments cleared on separate settlement vouchers.
-• Test 4 (Off-Hours GL): Isolates manual journal adjustments posted on weekends or outside 07:00 to 19:00 business hours.
-• Test 5 (Round-Sum Fees): Identifies flat-fee disbursements (&gt;= $5,000 divisible by $1,000 or $2,500) in high-risk discretionary accounts (Consulting, Legal, Marketing, Advisory).</t>
-  </si>
-  <si>
-    <t>5. REPORTING FINDINGS: THE EBITDA EXPOSURE STANDARD</t>
-  </si>
-  <si>
-    <t>Never report procedural compliance deficiencies (e.g. '3 out of 25 forms were missing second approval'). That format is routinely dismissed by CFOs as bureaucratic friction.</t>
-  </si>
-  <si>
-    <t>Frame findings through business impact:
-'Across 100% of FY26 procurement commitments ($42.8M spend), deterministic testing identified 14 purchase orders totaling $218,000 split below the $10,000 single-buyer DOA ceiling. Partitioning allowed department heads to bypass competitive bidding, resulting in an estimated 5–8% pricing premium over contracted supplier rate cards.'</t>
-  </si>
-  <si>
-    <t>FIELD TRIAGE RUBRIC: EVIDENCE RULES &amp; DIAGNOSTIC INQUIRY</t>
-  </si>
-  <si>
-    <t>Substantive Verification Standards for Flagged Transactions</t>
+    <t>1. PURPOSE &amp; SCOPE</t>
+  </si>
+  <si>
+    <t>This workbook executes automated exception testing across 100% of transaction populations in Procurement, Accounts Payable, and General Ledger. It identifies potential policy circumventions (split orders below delegation limits), master data changes (dormant vendor payment redirection), duplicate invoice disbursements, cutoff timing manipulations, and unsubstantiated round-sum service fees.</t>
+  </si>
+  <si>
+    <t>2. HOW TO INPUT CLIENT DATA (STEP-BY-STEP)</t>
+  </si>
+  <si>
+    <t>Step 1: Obtain Data</t>
+  </si>
+  <si>
+    <t>Request the required flat-file CSV extracts from IT/Finance using the exact column specifications in Tab '02_IT_Data_Request'.</t>
+  </si>
+  <si>
+    <t>Step 2: Clear Sample Data</t>
+  </si>
+  <si>
+    <t>Go to the target test tab (e.g. 'Test1_Split_POs'). Select the sample data cells in the INPUT columns (Columns with Navy Headers, Row 4 downward) and press Delete. IMPORTANT: Do NOT delete or clear the FORMULA columns (Columns with Slate Headers).</t>
+  </si>
+  <si>
+    <t>Step 3: Paste Raw Data</t>
+  </si>
+  <si>
+    <t>Copy your client's raw CSV extract, select Cell A4 in the target test tab, and paste (Ctrl + V). The Excel Table will expand automatically, and all formulas in adjacent columns will calculate instantly.</t>
+  </si>
+  <si>
+    <t>Step 4: Filter Exceptions</t>
+  </si>
+  <si>
+    <t>Filter the 'Audit_Flag' column for 'FLAG: ...'. Every flagged row is an exception requiring review.</t>
+  </si>
+  <si>
+    <t>Step 5: Review Summary</t>
+  </si>
+  <si>
+    <t>Navigate to Tab '99_Summary'. The executive dashboard updates dynamically via structured table references, displaying total exceptions and calculated financial exposure.</t>
+  </si>
+  <si>
+    <t>3. DATA INPUT &amp; COLUMN MAPPING MATRIX</t>
+  </si>
+  <si>
+    <t>Testing Tab</t>
+  </si>
+  <si>
+    <t>Source Data Required</t>
+  </si>
+  <si>
+    <t>Data Input Columns (Paste Here)</t>
+  </si>
+  <si>
+    <t>Formula Columns (Do Not Overwrite)</t>
+  </si>
+  <si>
+    <t>Primary Exception Tested</t>
+  </si>
+  <si>
+    <t>Test1_Split_POs</t>
+  </si>
+  <si>
+    <t>PO Line Items Extract</t>
+  </si>
+  <si>
+    <t>Cols A – H (PO_Number to PO_Status)</t>
+  </si>
+  <si>
+    <t>Cols I – M (Window Count, Total, Flag, Exposure)</t>
+  </si>
+  <si>
+    <t>POs split &lt; $10k limit within 5 days</t>
+  </si>
+  <si>
+    <t>Test2_Dormant_Vendors</t>
+  </si>
+  <si>
+    <t>Vendor Master &amp; AP Payments</t>
+  </si>
+  <si>
+    <t>Cols A – G (Vendor_ID to Bank_Account_IBAN)</t>
+  </si>
+  <si>
+    <t>Cols H – L (Days Dormant, Bank Update, Flag, Exposure)</t>
+  </si>
+  <si>
+    <t>Dormant &gt;180 days with recent bank change &lt;=30d</t>
+  </si>
+  <si>
+    <t>Test3_Duplicate_Invoices</t>
+  </si>
+  <si>
+    <t>AP Invoices Register</t>
+  </si>
+  <si>
+    <t>Cols A – C &amp; Cols E – H</t>
+  </si>
+  <si>
+    <t>Col D (Clean String) &amp; Cols I – L (Match, Flag, Exposure)</t>
+  </si>
+  <si>
+    <t>Near-duplicate invoices bypassing ERP punctuation checks</t>
+  </si>
+  <si>
+    <t>Test4_Off_Hours_GL</t>
+  </si>
+  <si>
+    <t>General Ledger Journal Lines</t>
+  </si>
+  <si>
+    <t>Cols A – G (Journal_ID to Post_Timestamp)</t>
+  </si>
+  <si>
+    <t>Cols H – N (Weekend/Time calculations, Flag, Exposure)</t>
+  </si>
+  <si>
+    <t>Manual adjustments posted weekends or 19:00 - 07:00</t>
+  </si>
+  <si>
+    <t>Test5_Round_Sum_Services</t>
+  </si>
+  <si>
+    <t>AP Invoice Line Items</t>
+  </si>
+  <si>
+    <t>Cols A – F (Invoice_ID to Created_By)</t>
+  </si>
+  <si>
+    <t>Cols G – L (Divisibility checks, High-Risk GL, Flag, Exposure)</t>
+  </si>
+  <si>
+    <t>Round fees &gt;= $5k divisible by $1k/$2.5k in Consulting/Legal</t>
+  </si>
+  <si>
+    <t>4. WORKPAPER STANDARDS &amp; REPORTING</t>
+  </si>
+  <si>
+    <t>• Trace Exceptions to Root Cause: An exception flag represents an audit anomaly, not automatic misconduct. Distinguish between operational coping mechanisms (e.g. buyers splitting orders to prevent delivery shutdowns) and intentional policy evasion.
+• Quantify Financial Exposure: Report findings using annualized exposure and price variance estimates rather than reporting sample defect percentages.
+• Remediation Focus: Recommend automated ERP system controls (such as requisition consolidation checks and dual-approval bank change gates) rather than mandating additional manual paper checklists.</t>
+  </si>
+  <si>
+    <t>FIELDWORK AUDIT PROCEDURES &amp; INQUIRY RUBRIC</t>
+  </si>
+  <si>
+    <t>Substantive Verification Standards &amp; Resolution Criteria for Flagged Exceptions</t>
   </si>
   <si>
     <t>Framework Architect: Majid Mumtaz (CIA, ACA, FCCA, GRCP, GRCA, COSO ERM)</t>
@@ -220,7 +313,7 @@
     <t>Recommend immediate suspension of recurring retainer until independent verification of work delivered is completed.</t>
   </si>
   <si>
-    <t>OPERATIONAL STANDARD: 100% Population Telemetry Replaces Sample Checklists. Do not sample 25 random invoices. Test all transactions, isolate anomalies, and audit the exceptions.</t>
+    <t>PROCEDURE STANDARD: Test full transaction populations deterministically, isolate exceptions, and verify underlying documentation.</t>
   </si>
   <si>
     <t>DATA EXTRACTION SPECIFICATION FOR IT &amp; DATABASE ADMINISTRATORS</t>
@@ -497,10 +590,10 @@
     <t>Journal line narration / transaction justification</t>
   </si>
   <si>
-    <t>ANOMALY TEST 1: SPLIT PURCHASE ORDERS (&lt; $10,000 THRESHOLD CIRCUMVENTION)</t>
-  </si>
-  <si>
-    <t>Identifies POs partitioned under $10,000 limit issued within 5 days to same vendor by same buyer (Sum &gt;= $10,000)</t>
+    <t>TEST 1: SPLIT PURCHASE ORDERS (&lt; $10,000 LIMIT)</t>
+  </si>
+  <si>
+    <t>INSTRUCTIONS: Paste raw PO lines into Columns A to H starting at Cell A4. Do NOT overwrite Columns I to M (Formulas calculate automatically).</t>
   </si>
   <si>
     <t>Buyer_ID</t>
@@ -725,10 +818,10 @@
     <t>TOTAL PORTFOLIO:</t>
   </si>
   <si>
-    <t>ANOMALY TEST 2: DORMANT VENDOR RESUSCITATION &amp; BANK ALTERATION AUDIT</t>
-  </si>
-  <si>
-    <t>Flags disbursements to vendors dormant for &gt;180 days with bank account updates within 30 days prior to payment</t>
+    <t>TEST 2: DORMANT VENDOR RESUSCITATION &amp; BANK ALTERATION</t>
+  </si>
+  <si>
+    <t>INSTRUCTIONS: Paste raw vendor payments into Columns A to G starting at Cell A4. Do NOT overwrite Columns H to L (Formulas calculate automatically).</t>
   </si>
   <si>
     <t>Payment_Amount</t>
@@ -863,10 +956,10 @@
     <t>Dormant 351 days, but bank update occurred 157 days ago (&gt;30d). Controlled reinstatement.</t>
   </si>
   <si>
-    <t>ANOMALY TEST 3: NEAR-DUPLICATE INVOICES (PUNCTUATION &amp; FORMAT STRIPPING)</t>
-  </si>
-  <si>
-    <t>Detects duplicate AP invoices bypassing ERP controls via punctuation alterations (e.g. 'INV-8842' vs 'INV 8842')</t>
+    <t>TEST 3: NEAR-DUPLICATE INVOICE VERIFICATION</t>
+  </si>
+  <si>
+    <t>INSTRUCTIONS: Paste raw AP invoices into Columns A:C and E:H starting at Cell A4. Do NOT overwrite Column D or Columns I:L (Formulas calculate automatically).</t>
   </si>
   <si>
     <t>Raw_Invoice_Number</t>
@@ -1025,10 +1118,10 @@
     <t>Unique invoice 'sec5501'; monthly security guarding services.</t>
   </si>
   <si>
-    <t>ANOMALY TEST 4: OFF-HOURS &amp; WEEKEND GENERAL LEDGER POSTINGS</t>
-  </si>
-  <si>
-    <t>Isolates manual journal entries posted on weekends or outside 7:00 AM - 7:00 PM business hours (Cutoff &amp; Deferral Evasion)</t>
+    <t>TEST 4: OFF-HOURS &amp; WEEKEND GENERAL LEDGER POSTINGS</t>
+  </si>
+  <si>
+    <t>INSTRUCTIONS: Paste raw GL journal entries into Columns A to G starting at Cell A4. Do NOT overwrite Columns H to N (Formulas calculate automatically).</t>
   </si>
   <si>
     <t>Day_of_Week</t>
@@ -1199,10 +1292,10 @@
     <t>Normal business hours entry (Monday 11:15 AM). Direct catering revenue recognition.</t>
   </si>
   <si>
-    <t>ANOMALY TEST 5: SUSPICIOUS ROUND-SUM PROFESSIONAL FEES &amp; SERVICES</t>
-  </si>
-  <si>
-    <t>Flags flat round-sum invoices (&gt;= $5,000 divisible by $1,000 or $2,500) in high-risk discretionary accounts</t>
+    <t>TEST 5: ROUND-SUM PROFESSIONAL FEES &amp; SERVICES</t>
+  </si>
+  <si>
+    <t>INSTRUCTIONS: Paste raw AP invoice lines into Columns A to F starting at Cell A4. Do NOT overwrite Columns G to L (Formulas calculate automatically).</t>
   </si>
   <si>
     <t>Invoice_ID</t>
@@ -1418,13 +1511,13 @@
     <t>Fixed hardware lease; routine capital equipment commitment.</t>
   </si>
   <si>
-    <t>CONTINUOUS CONTROLS MONITORING: EXCEPTION &amp; EXPOSURE REGISTER</t>
-  </si>
-  <si>
-    <t>Aggregated Population Telemetry &amp; Financial Exposure Summary | 100% Population Testing</t>
-  </si>
-  <si>
-    <t>ENGAGEMENT METADATA &amp; TELEMETRY PARAMETERS</t>
+    <t>INTERNAL AUDIT EXCEPTION SUMMARY &amp; EXPOSURE REGISTER</t>
+  </si>
+  <si>
+    <t>Automated Population Testing Results: Procurement, Accounts Payable &amp; General Ledger</t>
+  </si>
+  <si>
+    <t>ENGAGEMENT METADATA &amp; PARAMETERS</t>
   </si>
   <si>
     <t>Audit Period:</t>
@@ -1439,25 +1532,16 @@
     <t>Internal Audit &amp; Risk Advisory</t>
   </si>
   <si>
-    <t>Target Population:</t>
-  </si>
-  <si>
-    <t>100% AP, PO Lines &amp; GL Journals</t>
-  </si>
-  <si>
-    <t>Audit Method:</t>
-  </si>
-  <si>
-    <t>Deterministic Continuous Anomaly Scanning</t>
-  </si>
-  <si>
-    <t>Framework Architect:</t>
-  </si>
-  <si>
-    <t>Majid Mumtaz | CIA, ACA (ICAEW), FCCA, GRCP, GRCA, COSO ERM</t>
-  </si>
-  <si>
-    <t>Author Profiles:</t>
+    <t>Scope:</t>
+  </si>
+  <si>
+    <t>100% Population of AP Invoices, PO Line Items &amp; GL Journals</t>
+  </si>
+  <si>
+    <t>Methodology:</t>
+  </si>
+  <si>
+    <t>Automated Continuous Control Exception Testing</t>
   </si>
   <si>
     <t>PORTFOLIO SUMMARY METRICS</t>
@@ -1565,22 +1649,22 @@
     <t>PORTFOLIO TOTAL:</t>
   </si>
   <si>
-    <t>EXECUTIVE COMMENTARY: THE PARALLAX VIEW ON OPERATIONAL BREAKDOWNS</t>
-  </si>
-  <si>
-    <t>1. Frontline Reality vs. Board Perception (The Structural Gap):</t>
-  </si>
-  <si>
-    <t>What appears to the Board Audit Committee as 'unauthorized evasion' is frequently a rational coping mechanism adopted by frontline managers under intense operational pressure. When ERP approval workflows impose a 72-hour bottleneck on simple operational repairs, department buyers split purchase orders under $10,000 to keep facilities running. Similarly, finance clerks posting journal adjustments at 11:45 PM on month-end close night are not executing fraud; they are coping with fragmented interfaces to meet reporting deadlines.</t>
+    <t>EXECUTIVE AUDIT COMMENTARY: OPERATIONAL OBSERVATIONS</t>
+  </si>
+  <si>
+    <t>1. Operational Context vs. Policy Non-Compliance:</t>
+  </si>
+  <si>
+    <t>Exceptions identified in continuous testing frequently reflect operational coping mechanisms rather than intentional evasion. When procurement approval workflows create bottlenecks during urgent maintenance or stock shortages, department buyers frequently split purchase orders under $10,000 to keep facilities running. Similarly, manual journal entries posted late at night typically reflect finance teams working against month-end reporting deadlines under fragmented subledger interfaces.</t>
   </si>
   <si>
     <t>Similarly, finance clerks posting journal adjustments at 11:45 PM on month-end close night are not executing fraud; they are struggling against fragmented subledger interfaces to hit executive reporting deadlines.</t>
   </si>
   <si>
-    <t>2. Remediation Must Address Structural Bottlenecks, Not Add Checklists:</t>
-  </si>
-  <si>
-    <t>Mandating more paper signatures or punitive memos drives workarounds into offline spreadsheets and WhatsApp groups. The sustainable remedy is automated controls built directly into system logic: automated order consolidation at the requisition gate, mandatory two-party verification gates on bank account updates, and automated duplicate string normalization at invoice entry.</t>
+    <t>2. Remediation Focus:</t>
+  </si>
+  <si>
+    <t>Audit remediation must address underlying operational friction. Mandating additional manual signatures or punitive memos often forces workarounds deeper into unmonitored spreadsheets and messaging channels. Sustainable remediation requires automated preventative controls: automated purchase order consolidation at requisition entry, mandatory out-of-band dual approval gates on bank account master changes, and automated duplicate string normalization.</t>
   </si>
 </sst>
 </file>
@@ -1593,25 +1677,13 @@
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Segoe UI"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9.5"/>
-      <color rgb="FFD9E1F2"/>
-      <name val="Segoe UI"/>
     </font>
     <font>
       <b/>
@@ -1708,13 +1780,54 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FFE2E8F0"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1B365D"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF0F172A"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0A58CA"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0F172A"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF1E293B"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1747,12 +1860,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2F5597"/>
-        <bgColor rgb="FF2F5597"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F4F8"/>
         <bgColor rgb="FFF2F4F8"/>
       </patternFill>
@@ -1771,12 +1878,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2E8F0"/>
-        <bgColor rgb="FFE2E8F0"/>
+        <fgColor rgb="FF1B365D"/>
+        <bgColor rgb="FF1B365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24416B"/>
+        <bgColor rgb="FF24416B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF6FF"/>
+        <bgColor rgb="FFEFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F5F9"/>
+        <bgColor rgb="FFF1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF475569"/>
+        <bgColor rgb="FF475569"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1903,168 +2034,202 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="8" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6524,167 +6689,323 @@
   <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="110" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="57" t="s">
+    <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="55" t="s">
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+    </row>
+    <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="45" t="s">
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+    </row>
+    <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="43"/>
+      <c r="B3" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="46" t="s">
+      <c r="C3" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="46" t="s">
+      <c r="D3" s="52" t="s">
         <v>4</v>
       </c>
+      <c r="E3" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="54" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="4" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="47" t="s">
-        <v>5</v>
-      </c>
+      <c r="A4" s="44"/>
     </row>
     <row r="5" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="48" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="48" t="s">
+      <c r="A5" s="45"/>
+      <c r="B5" s="52" t="s">
         <v>7</v>
       </c>
     </row>
+    <row r="6" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="45"/>
+      <c r="B6" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+    </row>
     <row r="7" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="48" t="s">
-        <v>8</v>
-      </c>
+      <c r="A7" s="45"/>
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="43"/>
-    </row>
-    <row r="9" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="49" t="s">
+      <c r="A8" s="41"/>
+      <c r="B8" s="52" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="55" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="48" t="s">
+    <row r="9" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="46"/>
+      <c r="B9" s="53" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="47" t="s">
+      <c r="C9" s="63" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="49" t="s">
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="64"/>
+    </row>
+    <row r="10" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="45"/>
+      <c r="B10" s="53" t="s">
         <v>12</v>
       </c>
+      <c r="C10" s="63" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+    </row>
+    <row r="11" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="63" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+    </row>
+    <row r="12" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="44"/>
+      <c r="B12" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="63" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+    </row>
+    <row r="13" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="46"/>
+      <c r="B13" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="63" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
     </row>
     <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="43"/>
+      <c r="A14" s="41"/>
     </row>
     <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="49" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="55" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="48" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="43"/>
-    </row>
-    <row r="18" spans="1:1" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="50" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="51" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" ht="55" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="48" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="43"/>
-    </row>
-    <row r="22" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="43"/>
-    </row>
-    <row r="23" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="43"/>
-    </row>
-    <row r="24" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="43"/>
-    </row>
-    <row r="25" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="43"/>
-    </row>
-    <row r="26" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="43"/>
-    </row>
-    <row r="28" spans="1:1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="44"/>
-    </row>
-    <row r="29" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="43"/>
-    </row>
-    <row r="30" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="43"/>
-    </row>
-    <row r="31" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="43"/>
-    </row>
-    <row r="32" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="43"/>
+      <c r="A15" s="46"/>
+      <c r="B15" s="52" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="45"/>
+      <c r="B16" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" s="55" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="41"/>
+      <c r="B17" s="56" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="59" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" s="57" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="47"/>
+      <c r="B18" s="56" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="58" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="59" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" s="57" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="48"/>
+      <c r="B19" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="57" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19" s="57" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="45"/>
+      <c r="B20" s="56" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="57" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="58" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="59" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="57" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="41"/>
+      <c r="B21" s="56" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="57" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" s="58" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="59" t="s">
+        <v>49</v>
+      </c>
+      <c r="F21" s="57" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="41"/>
+    </row>
+    <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="41"/>
+      <c r="B23" s="52" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="41"/>
+      <c r="B24" s="63" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="64"/>
+      <c r="D24" s="64"/>
+      <c r="E24" s="64"/>
+      <c r="F24" s="64"/>
+    </row>
+    <row r="25" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="41"/>
+    </row>
+    <row r="26" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="41"/>
+    </row>
+    <row r="28" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="42"/>
+    </row>
+    <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="41"/>
+    </row>
+    <row r="30" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="41"/>
+    </row>
+    <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="41"/>
+    </row>
+    <row r="32" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="41"/>
     </row>
     <row r="33" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="43"/>
+      <c r="A33" s="41"/>
     </row>
     <row r="35" spans="1:1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="44"/>
+      <c r="A35" s="42"/>
     </row>
     <row r="36" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="43"/>
+      <c r="A36" s="41"/>
     </row>
     <row r="37" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="43"/>
+      <c r="A37" s="41"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="9">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C13:F13"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B24:F24"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="E3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="F3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6704,165 +7025,165 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="57" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
+      <c r="A1" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
+      <c r="A2" s="67" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="40" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="41" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="41" t="s">
-        <v>4</v>
+      <c r="A3" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="39" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="52" t="s">
-        <v>31</v>
+        <v>64</v>
+      </c>
+      <c r="D5" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="49" t="s">
+        <v>66</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="53" t="s">
-        <v>37</v>
+        <v>70</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="50" t="s">
+        <v>72</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" s="52" t="s">
-        <v>43</v>
+        <v>76</v>
+      </c>
+      <c r="D7" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="49" t="s">
+        <v>78</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="53" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="53" t="s">
-        <v>49</v>
+        <v>82</v>
+      </c>
+      <c r="D8" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>84</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="52" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" s="52" t="s">
-        <v>55</v>
+        <v>88</v>
+      </c>
+      <c r="D9" s="49" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" s="49" t="s">
+        <v>90</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="58" t="s">
-        <v>57</v>
-      </c>
-      <c r="B11" s="56"/>
-      <c r="C11" s="56"/>
-      <c r="D11" s="56"/>
-      <c r="E11" s="56"/>
-      <c r="F11" s="56"/>
+      <c r="A11" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" s="64"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -6890,674 +7211,674 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="57" t="s">
-        <v>58</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
+      <c r="A1" s="78" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="55" t="s">
-        <v>59</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
+      <c r="A2" s="80" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="40" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="41" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="41" t="s">
-        <v>4</v>
+      <c r="A3" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="39" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="67" t="s">
-        <v>60</v>
-      </c>
-      <c r="B4" s="56"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
+      <c r="A4" s="79" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
     </row>
     <row r="5" spans="1:5" ht="145" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="68" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" s="60"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="61"/>
+      <c r="A5" s="81" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="71"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="72"/>
     </row>
     <row r="7" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="67" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="56"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
+      <c r="A7" s="79" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
     </row>
     <row r="8" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="63" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="56"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
+      <c r="A8" s="74" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" s="64"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
     </row>
     <row r="9" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="64" t="s">
-        <v>66</v>
-      </c>
-      <c r="D9" s="65"/>
-      <c r="E9" s="66"/>
+        <v>100</v>
+      </c>
+      <c r="C9" s="75" t="s">
+        <v>101</v>
+      </c>
+      <c r="D9" s="76"/>
+      <c r="E9" s="77"/>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="7" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" s="59" t="s">
-        <v>69</v>
-      </c>
-      <c r="D10" s="60"/>
-      <c r="E10" s="61"/>
+        <v>103</v>
+      </c>
+      <c r="C10" s="70" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" s="71"/>
+      <c r="E10" s="72"/>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="9" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" s="62" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" s="60"/>
-      <c r="E11" s="61"/>
+        <v>106</v>
+      </c>
+      <c r="C11" s="73" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11" s="71"/>
+      <c r="E11" s="72"/>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="7" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" s="59" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" s="60"/>
-      <c r="E12" s="61"/>
+        <v>106</v>
+      </c>
+      <c r="C12" s="70" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" s="71"/>
+      <c r="E12" s="72"/>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="9" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" s="62" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="61"/>
+        <v>111</v>
+      </c>
+      <c r="C13" s="73" t="s">
+        <v>112</v>
+      </c>
+      <c r="D13" s="71"/>
+      <c r="E13" s="72"/>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="7" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" s="59" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" s="60"/>
-      <c r="E14" s="61"/>
+        <v>114</v>
+      </c>
+      <c r="C14" s="70" t="s">
+        <v>115</v>
+      </c>
+      <c r="D14" s="71"/>
+      <c r="E14" s="72"/>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="9" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" s="62" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" s="60"/>
-      <c r="E15" s="61"/>
+        <v>106</v>
+      </c>
+      <c r="C15" s="73" t="s">
+        <v>117</v>
+      </c>
+      <c r="D15" s="71"/>
+      <c r="E15" s="72"/>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="7" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" s="59" t="s">
-        <v>84</v>
-      </c>
-      <c r="D16" s="60"/>
-      <c r="E16" s="61"/>
+        <v>111</v>
+      </c>
+      <c r="C16" s="70" t="s">
+        <v>119</v>
+      </c>
+      <c r="D16" s="71"/>
+      <c r="E16" s="72"/>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="9" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" s="62" t="s">
-        <v>86</v>
-      </c>
-      <c r="D17" s="60"/>
-      <c r="E17" s="61"/>
+        <v>106</v>
+      </c>
+      <c r="C17" s="73" t="s">
+        <v>121</v>
+      </c>
+      <c r="D17" s="71"/>
+      <c r="E17" s="72"/>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="7" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" s="59" t="s">
-        <v>88</v>
-      </c>
-      <c r="D18" s="60"/>
-      <c r="E18" s="61"/>
+        <v>106</v>
+      </c>
+      <c r="C18" s="70" t="s">
+        <v>123</v>
+      </c>
+      <c r="D18" s="71"/>
+      <c r="E18" s="72"/>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="9" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" s="62" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" s="60"/>
-      <c r="E19" s="61"/>
+        <v>106</v>
+      </c>
+      <c r="C19" s="73" t="s">
+        <v>125</v>
+      </c>
+      <c r="D19" s="71"/>
+      <c r="E19" s="72"/>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="7" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" s="59" t="s">
-        <v>92</v>
-      </c>
-      <c r="D20" s="60"/>
-      <c r="E20" s="61"/>
+        <v>106</v>
+      </c>
+      <c r="C20" s="70" t="s">
+        <v>127</v>
+      </c>
+      <c r="D20" s="71"/>
+      <c r="E20" s="72"/>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="9" t="s">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C21" s="62" t="s">
-        <v>94</v>
-      </c>
-      <c r="D21" s="60"/>
-      <c r="E21" s="61"/>
+        <v>106</v>
+      </c>
+      <c r="C21" s="73" t="s">
+        <v>129</v>
+      </c>
+      <c r="D21" s="71"/>
+      <c r="E21" s="72"/>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="7" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="C22" s="59" t="s">
-        <v>97</v>
-      </c>
-      <c r="D22" s="60"/>
-      <c r="E22" s="61"/>
+        <v>131</v>
+      </c>
+      <c r="C22" s="70" t="s">
+        <v>132</v>
+      </c>
+      <c r="D22" s="71"/>
+      <c r="E22" s="72"/>
     </row>
     <row r="23" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="67" t="s">
-        <v>98</v>
-      </c>
-      <c r="B23" s="56"/>
-      <c r="C23" s="56"/>
-      <c r="D23" s="56"/>
-      <c r="E23" s="56"/>
+      <c r="A23" s="79" t="s">
+        <v>133</v>
+      </c>
+      <c r="B23" s="64"/>
+      <c r="C23" s="64"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="64"/>
     </row>
     <row r="24" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="63" t="s">
-        <v>99</v>
-      </c>
-      <c r="B24" s="56"/>
-      <c r="C24" s="56"/>
-      <c r="D24" s="56"/>
-      <c r="E24" s="56"/>
+      <c r="A24" s="74" t="s">
+        <v>134</v>
+      </c>
+      <c r="B24" s="64"/>
+      <c r="C24" s="64"/>
+      <c r="D24" s="64"/>
+      <c r="E24" s="64"/>
     </row>
     <row r="25" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C25" s="64" t="s">
-        <v>66</v>
-      </c>
-      <c r="D25" s="65"/>
-      <c r="E25" s="66"/>
+        <v>100</v>
+      </c>
+      <c r="C25" s="75" t="s">
+        <v>101</v>
+      </c>
+      <c r="D25" s="76"/>
+      <c r="E25" s="77"/>
     </row>
     <row r="26" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="7" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C26" s="59" t="s">
-        <v>101</v>
-      </c>
-      <c r="D26" s="60"/>
-      <c r="E26" s="61"/>
+        <v>106</v>
+      </c>
+      <c r="C26" s="70" t="s">
+        <v>136</v>
+      </c>
+      <c r="D26" s="71"/>
+      <c r="E26" s="72"/>
     </row>
     <row r="27" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="9" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="C27" s="62" t="s">
-        <v>104</v>
-      </c>
-      <c r="D27" s="60"/>
-      <c r="E27" s="61"/>
+        <v>138</v>
+      </c>
+      <c r="C27" s="73" t="s">
+        <v>139</v>
+      </c>
+      <c r="D27" s="71"/>
+      <c r="E27" s="72"/>
     </row>
     <row r="28" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="7" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" s="59" t="s">
-        <v>69</v>
-      </c>
-      <c r="D28" s="60"/>
-      <c r="E28" s="61"/>
+        <v>103</v>
+      </c>
+      <c r="C28" s="70" t="s">
+        <v>104</v>
+      </c>
+      <c r="D28" s="71"/>
+      <c r="E28" s="72"/>
     </row>
     <row r="29" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="9" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C29" s="62" t="s">
-        <v>105</v>
-      </c>
-      <c r="D29" s="60"/>
-      <c r="E29" s="61"/>
+        <v>106</v>
+      </c>
+      <c r="C29" s="73" t="s">
+        <v>140</v>
+      </c>
+      <c r="D29" s="71"/>
+      <c r="E29" s="72"/>
     </row>
     <row r="30" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="7" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" s="59" t="s">
-        <v>107</v>
-      </c>
-      <c r="D30" s="60"/>
-      <c r="E30" s="61"/>
+        <v>111</v>
+      </c>
+      <c r="C30" s="70" t="s">
+        <v>142</v>
+      </c>
+      <c r="D30" s="71"/>
+      <c r="E30" s="72"/>
     </row>
     <row r="31" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="9" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C31" s="62" t="s">
-        <v>109</v>
-      </c>
-      <c r="D31" s="60"/>
-      <c r="E31" s="61"/>
+        <v>114</v>
+      </c>
+      <c r="C31" s="73" t="s">
+        <v>144</v>
+      </c>
+      <c r="D31" s="71"/>
+      <c r="E31" s="72"/>
     </row>
     <row r="32" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="7" t="s">
-        <v>110</v>
+        <v>145</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C32" s="59" t="s">
-        <v>111</v>
-      </c>
-      <c r="D32" s="60"/>
-      <c r="E32" s="61"/>
+        <v>106</v>
+      </c>
+      <c r="C32" s="70" t="s">
+        <v>146</v>
+      </c>
+      <c r="D32" s="71"/>
+      <c r="E32" s="72"/>
     </row>
     <row r="33" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="9" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C33" s="62" t="s">
-        <v>112</v>
-      </c>
-      <c r="D33" s="60"/>
-      <c r="E33" s="61"/>
+        <v>106</v>
+      </c>
+      <c r="C33" s="73" t="s">
+        <v>147</v>
+      </c>
+      <c r="D33" s="71"/>
+      <c r="E33" s="72"/>
     </row>
     <row r="34" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="7" t="s">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C34" s="59" t="s">
-        <v>113</v>
-      </c>
-      <c r="D34" s="60"/>
-      <c r="E34" s="61"/>
+        <v>106</v>
+      </c>
+      <c r="C34" s="70" t="s">
+        <v>148</v>
+      </c>
+      <c r="D34" s="71"/>
+      <c r="E34" s="72"/>
     </row>
     <row r="35" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="9" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C35" s="62" t="s">
-        <v>115</v>
-      </c>
-      <c r="D35" s="60"/>
-      <c r="E35" s="61"/>
+        <v>106</v>
+      </c>
+      <c r="C35" s="73" t="s">
+        <v>150</v>
+      </c>
+      <c r="D35" s="71"/>
+      <c r="E35" s="72"/>
     </row>
     <row r="36" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="67" t="s">
-        <v>116</v>
-      </c>
-      <c r="B36" s="56"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="E36" s="56"/>
+      <c r="A36" s="79" t="s">
+        <v>151</v>
+      </c>
+      <c r="B36" s="64"/>
+      <c r="C36" s="64"/>
+      <c r="D36" s="64"/>
+      <c r="E36" s="64"/>
     </row>
     <row r="37" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="63" t="s">
-        <v>117</v>
-      </c>
-      <c r="B37" s="56"/>
-      <c r="C37" s="56"/>
-      <c r="D37" s="56"/>
-      <c r="E37" s="56"/>
+      <c r="A37" s="74" t="s">
+        <v>152</v>
+      </c>
+      <c r="B37" s="64"/>
+      <c r="C37" s="64"/>
+      <c r="D37" s="64"/>
+      <c r="E37" s="64"/>
     </row>
     <row r="38" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C38" s="64" t="s">
-        <v>66</v>
-      </c>
-      <c r="D38" s="65"/>
-      <c r="E38" s="66"/>
+        <v>100</v>
+      </c>
+      <c r="C38" s="75" t="s">
+        <v>101</v>
+      </c>
+      <c r="D38" s="76"/>
+      <c r="E38" s="77"/>
     </row>
     <row r="39" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="7" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C39" s="59" t="s">
-        <v>69</v>
-      </c>
-      <c r="D39" s="60"/>
-      <c r="E39" s="61"/>
+        <v>103</v>
+      </c>
+      <c r="C39" s="70" t="s">
+        <v>104</v>
+      </c>
+      <c r="D39" s="71"/>
+      <c r="E39" s="72"/>
     </row>
     <row r="40" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="9" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C40" s="62" t="s">
-        <v>118</v>
-      </c>
-      <c r="D40" s="60"/>
-      <c r="E40" s="61"/>
+        <v>106</v>
+      </c>
+      <c r="C40" s="73" t="s">
+        <v>153</v>
+      </c>
+      <c r="D40" s="71"/>
+      <c r="E40" s="72"/>
     </row>
     <row r="41" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="7" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C41" s="59" t="s">
-        <v>120</v>
-      </c>
-      <c r="D41" s="60"/>
-      <c r="E41" s="61"/>
+        <v>106</v>
+      </c>
+      <c r="C41" s="70" t="s">
+        <v>155</v>
+      </c>
+      <c r="D41" s="71"/>
+      <c r="E41" s="72"/>
     </row>
     <row r="42" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="9" t="s">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C42" s="62" t="s">
-        <v>122</v>
-      </c>
-      <c r="D42" s="60"/>
-      <c r="E42" s="61"/>
+        <v>106</v>
+      </c>
+      <c r="C42" s="73" t="s">
+        <v>157</v>
+      </c>
+      <c r="D42" s="71"/>
+      <c r="E42" s="72"/>
     </row>
     <row r="43" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="7" t="s">
-        <v>123</v>
+        <v>158</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C43" s="59" t="s">
-        <v>124</v>
-      </c>
-      <c r="D43" s="60"/>
-      <c r="E43" s="61"/>
+        <v>111</v>
+      </c>
+      <c r="C43" s="70" t="s">
+        <v>159</v>
+      </c>
+      <c r="D43" s="71"/>
+      <c r="E43" s="72"/>
     </row>
     <row r="44" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="9" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C44" s="62" t="s">
-        <v>126</v>
-      </c>
-      <c r="D44" s="60"/>
-      <c r="E44" s="61"/>
+        <v>111</v>
+      </c>
+      <c r="C44" s="73" t="s">
+        <v>161</v>
+      </c>
+      <c r="D44" s="71"/>
+      <c r="E44" s="72"/>
     </row>
     <row r="45" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="67" t="s">
-        <v>127</v>
-      </c>
-      <c r="B45" s="56"/>
-      <c r="C45" s="56"/>
-      <c r="D45" s="56"/>
-      <c r="E45" s="56"/>
+      <c r="A45" s="79" t="s">
+        <v>162</v>
+      </c>
+      <c r="B45" s="64"/>
+      <c r="C45" s="64"/>
+      <c r="D45" s="64"/>
+      <c r="E45" s="64"/>
     </row>
     <row r="46" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="63" t="s">
-        <v>128</v>
-      </c>
-      <c r="B46" s="56"/>
-      <c r="C46" s="56"/>
-      <c r="D46" s="56"/>
-      <c r="E46" s="56"/>
+      <c r="A46" s="74" t="s">
+        <v>163</v>
+      </c>
+      <c r="B46" s="64"/>
+      <c r="C46" s="64"/>
+      <c r="D46" s="64"/>
+      <c r="E46" s="64"/>
     </row>
     <row r="47" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="6" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C47" s="64" t="s">
-        <v>66</v>
-      </c>
-      <c r="D47" s="65"/>
-      <c r="E47" s="66"/>
+        <v>100</v>
+      </c>
+      <c r="C47" s="75" t="s">
+        <v>101</v>
+      </c>
+      <c r="D47" s="76"/>
+      <c r="E47" s="77"/>
     </row>
     <row r="48" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="7" t="s">
-        <v>129</v>
+        <v>164</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C48" s="59" t="s">
-        <v>130</v>
-      </c>
-      <c r="D48" s="60"/>
-      <c r="E48" s="61"/>
+        <v>106</v>
+      </c>
+      <c r="C48" s="70" t="s">
+        <v>165</v>
+      </c>
+      <c r="D48" s="71"/>
+      <c r="E48" s="72"/>
     </row>
     <row r="49" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="9" t="s">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C49" s="62" t="s">
-        <v>132</v>
-      </c>
-      <c r="D49" s="60"/>
-      <c r="E49" s="61"/>
+        <v>106</v>
+      </c>
+      <c r="C49" s="73" t="s">
+        <v>167</v>
+      </c>
+      <c r="D49" s="71"/>
+      <c r="E49" s="72"/>
     </row>
     <row r="50" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="7" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C50" s="59" t="s">
-        <v>134</v>
-      </c>
-      <c r="D50" s="60"/>
-      <c r="E50" s="61"/>
+        <v>106</v>
+      </c>
+      <c r="C50" s="70" t="s">
+        <v>169</v>
+      </c>
+      <c r="D50" s="71"/>
+      <c r="E50" s="72"/>
     </row>
     <row r="51" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="9" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C51" s="62" t="s">
-        <v>136</v>
-      </c>
-      <c r="D51" s="60"/>
-      <c r="E51" s="61"/>
+        <v>114</v>
+      </c>
+      <c r="C51" s="73" t="s">
+        <v>171</v>
+      </c>
+      <c r="D51" s="71"/>
+      <c r="E51" s="72"/>
     </row>
     <row r="52" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="7" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C52" s="59" t="s">
-        <v>138</v>
-      </c>
-      <c r="D52" s="60"/>
-      <c r="E52" s="61"/>
+        <v>114</v>
+      </c>
+      <c r="C52" s="70" t="s">
+        <v>173</v>
+      </c>
+      <c r="D52" s="71"/>
+      <c r="E52" s="72"/>
     </row>
     <row r="53" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="9" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C53" s="62" t="s">
-        <v>139</v>
-      </c>
-      <c r="D53" s="60"/>
-      <c r="E53" s="61"/>
+        <v>106</v>
+      </c>
+      <c r="C53" s="73" t="s">
+        <v>174</v>
+      </c>
+      <c r="D53" s="71"/>
+      <c r="E53" s="72"/>
     </row>
     <row r="54" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="7" t="s">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="C54" s="59" t="s">
-        <v>141</v>
-      </c>
-      <c r="D54" s="60"/>
-      <c r="E54" s="61"/>
+        <v>131</v>
+      </c>
+      <c r="C54" s="70" t="s">
+        <v>176</v>
+      </c>
+      <c r="D54" s="71"/>
+      <c r="E54" s="72"/>
     </row>
     <row r="55" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="9" t="s">
-        <v>142</v>
+        <v>177</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C55" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D55" s="60"/>
-      <c r="E55" s="61"/>
+        <v>106</v>
+      </c>
+      <c r="C55" s="73" t="s">
+        <v>178</v>
+      </c>
+      <c r="D55" s="71"/>
+      <c r="E55" s="72"/>
     </row>
     <row r="56" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="7" t="s">
-        <v>144</v>
+        <v>179</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C56" s="59" t="s">
-        <v>145</v>
-      </c>
-      <c r="D56" s="60"/>
-      <c r="E56" s="61"/>
+        <v>106</v>
+      </c>
+      <c r="C56" s="70" t="s">
+        <v>180</v>
+      </c>
+      <c r="D56" s="71"/>
+      <c r="E56" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="54">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C13:E13"/>
     <mergeCell ref="C53:E53"/>
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="C49:E49"/>
@@ -7597,7 +7918,7 @@
     <mergeCell ref="C32:E32"/>
     <mergeCell ref="C38:E38"/>
     <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C19:E19"/>
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="C29:E29"/>
     <mergeCell ref="C20:E20"/>
@@ -7640,104 +7961,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
-        <v>146</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-    </row>
-    <row r="2" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="69" t="s">
-        <v>147</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-    </row>
-    <row r="3" spans="1:13" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="28" t="s">
-        <v>100</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>106</v>
-      </c>
-      <c r="C3" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="E3" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="F3" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="G3" s="28" t="s">
-        <v>110</v>
-      </c>
-      <c r="H3" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="I3" s="29" t="s">
+      <c r="A1" s="69" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+    </row>
+    <row r="2" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="82" t="s">
+        <v>182</v>
+      </c>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="64"/>
+    </row>
+    <row r="3" spans="1:13" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="60" t="s">
+        <v>135</v>
+      </c>
+      <c r="B3" s="60" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="60" t="s">
+        <v>105</v>
+      </c>
+      <c r="E3" s="60" t="s">
+        <v>183</v>
+      </c>
+      <c r="F3" s="60" t="s">
+        <v>143</v>
+      </c>
+      <c r="G3" s="60" t="s">
+        <v>145</v>
+      </c>
+      <c r="H3" s="60" t="s">
         <v>149</v>
       </c>
-      <c r="J3" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="K3" s="29" t="s">
-        <v>151</v>
-      </c>
-      <c r="L3" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="M3" s="28" t="s">
-        <v>153</v>
+      <c r="I3" s="61" t="s">
+        <v>184</v>
+      </c>
+      <c r="J3" s="61" t="s">
+        <v>185</v>
+      </c>
+      <c r="K3" s="61" t="s">
+        <v>186</v>
+      </c>
+      <c r="L3" s="61" t="s">
+        <v>187</v>
+      </c>
+      <c r="M3" s="61" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="7" t="s">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="B4" s="11">
         <v>46082</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>155</v>
+        <v>190</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>157</v>
+        <v>192</v>
       </c>
       <c r="F4" s="12">
         <v>8500</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>158</v>
+        <v>193</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="I4" s="13">
         <f t="shared" ref="I4:I18" si="0">IF(OR(F4&lt;=0, ISBLANK(F4), NOT(ISNUMBER(F4)), ISBLANK(B4)), 0, COUNTIFS($C:$C, C4, $E:$E, E4, $B:$B, "&gt;="&amp;(B4-5), $B:$B, "&lt;="&amp;(B4+5), $F:$F, "&gt;0", $F:$F, "&lt;10000"))</f>
@@ -7755,34 +8076,34 @@
         <f t="shared" ref="L4:L18" si="3">IF(K4="FLAG: SPLIT PO", F4, 0)</f>
         <v>8500</v>
       </c>
-      <c r="M4" s="54" t="s">
-        <v>160</v>
+      <c r="M4" s="51" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="7" t="s">
-        <v>161</v>
+        <v>196</v>
       </c>
       <c r="B5" s="11">
         <v>46084</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>155</v>
+        <v>190</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>157</v>
+        <v>192</v>
       </c>
       <c r="F5" s="12">
         <v>9000</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>162</v>
+        <v>197</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="I5" s="13">
         <f t="shared" si="0"/>
@@ -7800,34 +8121,34 @@
         <f t="shared" si="3"/>
         <v>9000</v>
       </c>
-      <c r="M5" s="54" t="s">
-        <v>163</v>
+      <c r="M5" s="51" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="7" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
       <c r="B6" s="11">
         <v>46091</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>166</v>
+        <v>201</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>167</v>
+        <v>202</v>
       </c>
       <c r="F6" s="12">
         <v>4800</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>168</v>
+        <v>203</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="I6" s="13">
         <f t="shared" si="0"/>
@@ -7845,34 +8166,34 @@
         <f t="shared" si="3"/>
         <v>4800</v>
       </c>
-      <c r="M6" s="54" t="s">
-        <v>169</v>
+      <c r="M6" s="51" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="7" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="B7" s="11">
         <v>46092</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>166</v>
+        <v>201</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>167</v>
+        <v>202</v>
       </c>
       <c r="F7" s="12">
         <v>4500</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>171</v>
+        <v>206</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="I7" s="13">
         <f t="shared" si="0"/>
@@ -7890,34 +8211,34 @@
         <f t="shared" si="3"/>
         <v>4500</v>
       </c>
-      <c r="M7" s="54" t="s">
-        <v>172</v>
+      <c r="M7" s="51" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="7" t="s">
-        <v>173</v>
+        <v>208</v>
       </c>
       <c r="B8" s="11">
         <v>46094</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>166</v>
+        <v>201</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>167</v>
+        <v>202</v>
       </c>
       <c r="F8" s="12">
         <v>4200</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>174</v>
+        <v>209</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="I8" s="13">
         <f t="shared" si="0"/>
@@ -7935,34 +8256,34 @@
         <f t="shared" si="3"/>
         <v>4200</v>
       </c>
-      <c r="M8" s="54" t="s">
-        <v>175</v>
+      <c r="M8" s="51" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="7" t="s">
-        <v>176</v>
+        <v>211</v>
       </c>
       <c r="B9" s="11">
         <v>46083</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>178</v>
+        <v>213</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>157</v>
+        <v>192</v>
       </c>
       <c r="F9" s="12">
         <v>45000</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="I9" s="13">
         <f t="shared" si="0"/>
@@ -7980,34 +8301,34 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M9" s="54" t="s">
-        <v>180</v>
+      <c r="M9" s="51" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="7" t="s">
-        <v>181</v>
+        <v>216</v>
       </c>
       <c r="B10" s="11">
         <v>46063</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>183</v>
+        <v>218</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>184</v>
+        <v>219</v>
       </c>
       <c r="F10" s="12">
         <v>3200</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="I10" s="13">
         <f t="shared" si="0"/>
@@ -8025,34 +8346,34 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M10" s="54" t="s">
-        <v>186</v>
+      <c r="M10" s="51" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="7" t="s">
-        <v>187</v>
+        <v>222</v>
       </c>
       <c r="B11" s="11">
         <v>46103</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>183</v>
+        <v>218</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>184</v>
+        <v>219</v>
       </c>
       <c r="F11" s="12">
         <v>4100</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>188</v>
+        <v>223</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="I11" s="13">
         <f t="shared" si="0"/>
@@ -8070,34 +8391,34 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M11" s="54" t="s">
-        <v>189</v>
+      <c r="M11" s="51" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="7" t="s">
-        <v>190</v>
+        <v>225</v>
       </c>
       <c r="B12" s="11">
         <v>46086</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>191</v>
+        <v>226</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>192</v>
+        <v>227</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>193</v>
+        <v>228</v>
       </c>
       <c r="F12" s="12">
         <v>2100</v>
       </c>
       <c r="G12" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="H12" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>159</v>
       </c>
       <c r="I12" s="13">
         <f t="shared" si="0"/>
@@ -8115,34 +8436,34 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M12" s="54" t="s">
-        <v>195</v>
+      <c r="M12" s="51" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="7" t="s">
-        <v>196</v>
+        <v>231</v>
       </c>
       <c r="B13" s="11">
         <v>46087</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>191</v>
+        <v>226</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>192</v>
+        <v>227</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>193</v>
+        <v>228</v>
       </c>
       <c r="F13" s="12">
         <v>2200</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>197</v>
+        <v>232</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="I13" s="13">
         <f t="shared" si="0"/>
@@ -8160,34 +8481,34 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M13" s="54" t="s">
-        <v>198</v>
+      <c r="M13" s="51" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="7" t="s">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="B14" s="11">
         <v>46089</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>155</v>
+        <v>190</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>167</v>
+        <v>202</v>
       </c>
       <c r="F14" s="12">
         <v>6500</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="I14" s="13">
         <f t="shared" si="0"/>
@@ -8206,33 +8527,33 @@
         <v>0</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>201</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="7" t="s">
-        <v>202</v>
+        <v>237</v>
       </c>
       <c r="B15" s="11">
         <v>46096</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>184</v>
+        <v>219</v>
       </c>
       <c r="F15" s="12">
         <v>9200</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="I15" s="13">
         <f t="shared" si="0"/>
@@ -8251,33 +8572,33 @@
         <v>0</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>206</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="7" t="s">
-        <v>207</v>
+        <v>242</v>
       </c>
       <c r="B16" s="11">
         <v>46106</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>208</v>
+        <v>243</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>209</v>
+        <v>244</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>193</v>
+        <v>228</v>
       </c>
       <c r="F16" s="12">
         <v>7800</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="I16" s="13">
         <f t="shared" si="0"/>
@@ -8296,33 +8617,33 @@
         <v>7800</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>211</v>
+        <v>246</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="7" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="B17" s="11">
         <v>46108</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>208</v>
+        <v>243</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>209</v>
+        <v>244</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>193</v>
+        <v>228</v>
       </c>
       <c r="F17" s="12">
         <v>7800</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>213</v>
+        <v>248</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="I17" s="13">
         <f t="shared" si="0"/>
@@ -8341,78 +8662,78 @@
         <v>7800</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>214</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="30" t="s">
-        <v>215</v>
-      </c>
-      <c r="B18" s="31">
+      <c r="A18" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="B18" s="29">
         <v>46110</v>
       </c>
-      <c r="C18" s="32" t="s">
-        <v>216</v>
-      </c>
-      <c r="D18" s="32" t="s">
-        <v>217</v>
-      </c>
-      <c r="E18" s="32" t="s">
-        <v>157</v>
-      </c>
-      <c r="F18" s="33">
+      <c r="C18" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="E18" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="F18" s="31">
         <v>9950</v>
       </c>
-      <c r="G18" s="32" t="s">
-        <v>218</v>
-      </c>
-      <c r="H18" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="I18" s="34">
+      <c r="G18" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="H18" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="I18" s="32">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J18" s="35">
+      <c r="J18" s="33">
         <f t="shared" si="1"/>
         <v>9950</v>
       </c>
-      <c r="K18" s="36" t="str">
+      <c r="K18" s="34" t="str">
         <f t="shared" si="2"/>
         <v>OK</v>
       </c>
-      <c r="L18" s="37">
+      <c r="L18" s="35">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M18" s="32" t="s">
-        <v>219</v>
+      <c r="M18" s="30" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32" t="s">
-        <v>221</v>
-      </c>
-      <c r="F19" s="33">
+      <c r="A19" s="28" t="s">
+        <v>255</v>
+      </c>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="F19" s="31">
         <f>SUBTOTAL(109,Table_Split_POs[PO_Amount])</f>
         <v>128850</v>
       </c>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="36"/>
-      <c r="L19" s="37">
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="36"/>
+      <c r="K19" s="34"/>
+      <c r="L19" s="35">
         <f>SUBTOTAL(109,Table_Split_POs[Financial_Exposure])</f>
         <v>46600</v>
       </c>
-      <c r="M19" s="32">
+      <c r="M19" s="30">
         <f>SUBTOTAL(103,Table_Split_POs[Audit_Workpaper_Notes])</f>
         <v>15</v>
       </c>
@@ -8454,81 +8775,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
-        <v>222</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-    </row>
-    <row r="2" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="69" t="s">
-        <v>223</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-    </row>
-    <row r="3" spans="1:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="E3" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="F3" s="28" t="s">
-        <v>224</v>
-      </c>
-      <c r="G3" s="28" t="s">
-        <v>225</v>
-      </c>
-      <c r="H3" s="29" t="s">
-        <v>226</v>
-      </c>
-      <c r="I3" s="29" t="s">
-        <v>227</v>
-      </c>
-      <c r="J3" s="29" t="s">
-        <v>151</v>
-      </c>
-      <c r="K3" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="L3" s="28" t="s">
-        <v>153</v>
+      <c r="A1" s="69" t="s">
+        <v>257</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+    </row>
+    <row r="2" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="82" t="s">
+        <v>258</v>
+      </c>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+    </row>
+    <row r="3" spans="1:12" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="60" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="60" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="60" t="s">
+        <v>160</v>
+      </c>
+      <c r="E3" s="60" t="s">
+        <v>158</v>
+      </c>
+      <c r="F3" s="60" t="s">
+        <v>259</v>
+      </c>
+      <c r="G3" s="60" t="s">
+        <v>260</v>
+      </c>
+      <c r="H3" s="61" t="s">
+        <v>261</v>
+      </c>
+      <c r="I3" s="61" t="s">
+        <v>262</v>
+      </c>
+      <c r="J3" s="61" t="s">
+        <v>186</v>
+      </c>
+      <c r="K3" s="61" t="s">
+        <v>187</v>
+      </c>
+      <c r="L3" s="61" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="7" t="s">
-        <v>228</v>
+        <v>263</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>229</v>
+        <v>264</v>
       </c>
       <c r="C4" s="11">
         <v>46127</v>
@@ -8543,7 +8864,7 @@
         <v>94200</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>230</v>
+        <v>265</v>
       </c>
       <c r="H4" s="13">
         <f t="shared" ref="H4:H13" si="0">IF(OR(ISBLANK(C4), ISBLANK(D4), D4=""), "", IF(ISNUMBER(C4), C4, IFERROR(DATEVALUE(C4), 0)) - IF(ISNUMBER(D4), D4, IFERROR(DATEVALUE(D4), 0)))</f>
@@ -8561,16 +8882,16 @@
         <f t="shared" ref="K4:K13" si="3">IF(J4="FLAG: DORMANT RESUSCITATION", IFERROR(VALUE(F4), F4), 0)</f>
         <v>94200</v>
       </c>
-      <c r="L4" s="54" t="s">
-        <v>231</v>
+      <c r="L4" s="51" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="7" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>233</v>
+        <v>268</v>
       </c>
       <c r="C5" s="11">
         <v>46130</v>
@@ -8585,7 +8906,7 @@
         <v>145000</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>234</v>
+        <v>269</v>
       </c>
       <c r="H5" s="13">
         <f t="shared" si="0"/>
@@ -8603,16 +8924,16 @@
         <f t="shared" si="3"/>
         <v>145000</v>
       </c>
-      <c r="L5" s="54" t="s">
-        <v>235</v>
+      <c r="L5" s="51" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="7" t="s">
-        <v>236</v>
+        <v>271</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>237</v>
+        <v>272</v>
       </c>
       <c r="C6" s="11">
         <v>46134</v>
@@ -8627,7 +8948,7 @@
         <v>38500</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>238</v>
+        <v>273</v>
       </c>
       <c r="H6" s="13">
         <f t="shared" si="0"/>
@@ -8645,16 +8966,16 @@
         <f t="shared" si="3"/>
         <v>38500</v>
       </c>
-      <c r="L6" s="54" t="s">
-        <v>239</v>
+      <c r="L6" s="51" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="7" t="s">
-        <v>240</v>
+        <v>275</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>241</v>
+        <v>276</v>
       </c>
       <c r="C7" s="11">
         <v>46140</v>
@@ -8669,7 +8990,7 @@
         <v>62000</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>242</v>
+        <v>277</v>
       </c>
       <c r="H7" s="13">
         <f t="shared" si="0"/>
@@ -8687,16 +9008,16 @@
         <f t="shared" si="3"/>
         <v>62000</v>
       </c>
-      <c r="L7" s="54" t="s">
-        <v>243</v>
+      <c r="L7" s="51" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="7" t="s">
-        <v>244</v>
+        <v>279</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>245</v>
+        <v>280</v>
       </c>
       <c r="C8" s="11">
         <v>46122</v>
@@ -8711,7 +9032,7 @@
         <v>54000</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>246</v>
+        <v>281</v>
       </c>
       <c r="H8" s="13">
         <f t="shared" si="0"/>
@@ -8729,16 +9050,16 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L8" s="54" t="s">
-        <v>247</v>
+      <c r="L8" s="51" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="7" t="s">
-        <v>248</v>
+        <v>283</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>249</v>
+        <v>284</v>
       </c>
       <c r="C9" s="11">
         <v>46124</v>
@@ -8753,7 +9074,7 @@
         <v>82500</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>250</v>
+        <v>285</v>
       </c>
       <c r="H9" s="13">
         <f t="shared" si="0"/>
@@ -8771,16 +9092,16 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L9" s="54" t="s">
-        <v>251</v>
+      <c r="L9" s="51" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="7" t="s">
-        <v>252</v>
+        <v>287</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>253</v>
+        <v>288</v>
       </c>
       <c r="C10" s="11">
         <v>46126</v>
@@ -8795,7 +9116,7 @@
         <v>118000</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>254</v>
+        <v>289</v>
       </c>
       <c r="H10" s="13">
         <f t="shared" si="0"/>
@@ -8813,16 +9134,16 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L10" s="54" t="s">
-        <v>255</v>
+      <c r="L10" s="51" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="7" t="s">
-        <v>256</v>
+        <v>291</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>257</v>
+        <v>292</v>
       </c>
       <c r="C11" s="11">
         <v>46128</v>
@@ -8837,7 +9158,7 @@
         <v>18900</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>258</v>
+        <v>293</v>
       </c>
       <c r="H11" s="13">
         <f t="shared" si="0"/>
@@ -8856,15 +9177,15 @@
         <v>0</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>259</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="7" t="s">
-        <v>260</v>
+        <v>295</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>261</v>
+        <v>296</v>
       </c>
       <c r="C12" s="11">
         <v>46137</v>
@@ -8879,7 +9200,7 @@
         <v>29400</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>262</v>
+        <v>297</v>
       </c>
       <c r="H12" s="13">
         <f t="shared" si="0"/>
@@ -8898,74 +9219,74 @@
         <v>0</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="30" t="s">
-        <v>264</v>
-      </c>
-      <c r="B13" s="32" t="s">
-        <v>265</v>
-      </c>
-      <c r="C13" s="31">
+      <c r="A13" s="28" t="s">
+        <v>299</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>300</v>
+      </c>
+      <c r="C13" s="29">
         <v>46138</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="29">
         <v>45787</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="29">
         <v>45981</v>
       </c>
-      <c r="F13" s="33">
+      <c r="F13" s="31">
         <v>47000</v>
       </c>
-      <c r="G13" s="32" t="s">
-        <v>266</v>
-      </c>
-      <c r="H13" s="34">
+      <c r="G13" s="30" t="s">
+        <v>301</v>
+      </c>
+      <c r="H13" s="32">
         <f t="shared" si="0"/>
         <v>351</v>
       </c>
-      <c r="I13" s="34">
+      <c r="I13" s="32">
         <f t="shared" si="1"/>
         <v>157</v>
       </c>
-      <c r="J13" s="36" t="str">
+      <c r="J13" s="34" t="str">
         <f t="shared" si="2"/>
         <v>OK</v>
       </c>
-      <c r="K13" s="37">
+      <c r="K13" s="35">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L13" s="32" t="s">
-        <v>267</v>
+      <c r="L13" s="30" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32" t="s">
-        <v>221</v>
-      </c>
-      <c r="F14" s="33">
+      <c r="A14" s="28" t="s">
+        <v>255</v>
+      </c>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="F14" s="31">
         <f>SUBTOTAL(109,Table_Dormant_Vendors[Payment_Amount])</f>
         <v>689500</v>
       </c>
-      <c r="G14" s="32"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="37">
+      <c r="G14" s="30"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="34"/>
+      <c r="K14" s="35">
         <f>SUBTOTAL(109,Table_Dormant_Vendors[Financial_Exposure])</f>
         <v>339700</v>
       </c>
-      <c r="L14" s="32">
+      <c r="L14" s="30">
         <f>SUBTOTAL(103,Table_Dormant_Vendors[Audit_Workpaper_Notes])</f>
         <v>10</v>
       </c>
@@ -9007,84 +9328,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
-        <v>268</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-    </row>
-    <row r="2" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="69" t="s">
-        <v>269</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-    </row>
-    <row r="3" spans="1:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" s="28" t="s">
-        <v>270</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="E3" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="F3" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="G3" s="28" t="s">
-        <v>272</v>
-      </c>
-      <c r="H3" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="I3" s="29" t="s">
-        <v>273</v>
-      </c>
-      <c r="J3" s="29" t="s">
-        <v>151</v>
-      </c>
-      <c r="K3" s="29" t="s">
-        <v>274</v>
-      </c>
-      <c r="L3" s="28" t="s">
-        <v>153</v>
+      <c r="A1" s="69" t="s">
+        <v>303</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+    </row>
+    <row r="2" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="82" t="s">
+        <v>304</v>
+      </c>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+    </row>
+    <row r="3" spans="1:12" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="60" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="60" t="s">
+        <v>305</v>
+      </c>
+      <c r="D3" s="61" t="s">
+        <v>306</v>
+      </c>
+      <c r="E3" s="61" t="s">
+        <v>110</v>
+      </c>
+      <c r="F3" s="61" t="s">
+        <v>113</v>
+      </c>
+      <c r="G3" s="61" t="s">
+        <v>307</v>
+      </c>
+      <c r="H3" s="61" t="s">
+        <v>118</v>
+      </c>
+      <c r="I3" s="61" t="s">
+        <v>308</v>
+      </c>
+      <c r="J3" s="61" t="s">
+        <v>186</v>
+      </c>
+      <c r="K3" s="61" t="s">
+        <v>309</v>
+      </c>
+      <c r="L3" s="61" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="7" t="s">
-        <v>275</v>
+        <v>310</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>276</v>
+        <v>311</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>277</v>
+        <v>312</v>
       </c>
       <c r="D4" s="13" t="str">
         <f t="shared" ref="D4:D15" si="0">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(C4)), "-", ""), "/", ""), " ", ""), ".", ""), "_", ""), "#", ""), ":", "")</f>
@@ -9097,7 +9418,7 @@
         <v>12850</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>278</v>
+        <v>313</v>
       </c>
       <c r="H4" s="11">
         <v>46099</v>
@@ -9114,19 +9435,19 @@
         <f>IF(AND(J4="FLAG: DUPLICATE INVOICE", COUNTIFS($A$4:INDEX($A:$A, ROW()), A4, $D$4:INDEX($D:$D, ROW()), D4, $F$4:INDEX($F:$F, ROW()), F4)&gt;1), IFERROR(VALUE(F4), F4), 0)</f>
         <v>0</v>
       </c>
-      <c r="L4" s="54" t="s">
-        <v>279</v>
+      <c r="L4" s="51" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="7" t="s">
-        <v>275</v>
+        <v>310</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>276</v>
+        <v>311</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>280</v>
+        <v>315</v>
       </c>
       <c r="D5" s="13" t="str">
         <f t="shared" si="0"/>
@@ -9139,7 +9460,7 @@
         <v>12850</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="H5" s="11">
         <v>46106</v>
@@ -9156,19 +9477,19 @@
         <f>IF(AND(J5="FLAG: DUPLICATE INVOICE", COUNTIFS($A$4:INDEX($A:$A, ROW()), A5, $D$4:INDEX($D:$D, ROW()), D5, $F$4:INDEX($F:$F, ROW()), F5)&gt;1), IFERROR(VALUE(F5), F5), 0)</f>
         <v>12850</v>
       </c>
-      <c r="L5" s="54" t="s">
-        <v>282</v>
+      <c r="L5" s="51" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="7" t="s">
-        <v>283</v>
+        <v>318</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>284</v>
+        <v>319</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>285</v>
+        <v>320</v>
       </c>
       <c r="D6" s="13" t="str">
         <f t="shared" si="0"/>
@@ -9181,7 +9502,7 @@
         <v>4750</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>286</v>
+        <v>321</v>
       </c>
       <c r="H6" s="11">
         <v>46103</v>
@@ -9198,19 +9519,19 @@
         <f>IF(AND(J6="FLAG: DUPLICATE INVOICE", COUNTIFS($A$4:INDEX($A:$A, ROW()), A6, $D$4:INDEX($D:$D, ROW()), D6, $F$4:INDEX($F:$F, ROW()), F6)&gt;1), IFERROR(VALUE(F6), F6), 0)</f>
         <v>0</v>
       </c>
-      <c r="L6" s="54" t="s">
-        <v>287</v>
+      <c r="L6" s="51" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="7" t="s">
-        <v>283</v>
+        <v>318</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>284</v>
+        <v>319</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>288</v>
+        <v>323</v>
       </c>
       <c r="D7" s="13" t="str">
         <f t="shared" si="0"/>
@@ -9223,7 +9544,7 @@
         <v>4750</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>289</v>
+        <v>324</v>
       </c>
       <c r="H7" s="11">
         <v>46110</v>
@@ -9240,19 +9561,19 @@
         <f>IF(AND(J7="FLAG: DUPLICATE INVOICE", COUNTIFS($A$4:INDEX($A:$A, ROW()), A7, $D$4:INDEX($D:$D, ROW()), D7, $F$4:INDEX($F:$F, ROW()), F7)&gt;1), IFERROR(VALUE(F7), F7), 0)</f>
         <v>4750</v>
       </c>
-      <c r="L7" s="54" t="s">
-        <v>290</v>
+      <c r="L7" s="51" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="7" t="s">
-        <v>291</v>
+        <v>326</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>292</v>
+        <v>327</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>293</v>
+        <v>328</v>
       </c>
       <c r="D8" s="13" t="str">
         <f t="shared" si="0"/>
@@ -9265,7 +9586,7 @@
         <v>28000</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>294</v>
+        <v>329</v>
       </c>
       <c r="H8" s="11">
         <v>46109</v>
@@ -9282,19 +9603,19 @@
         <f>IF(AND(J8="FLAG: DUPLICATE INVOICE", COUNTIFS($A$4:INDEX($A:$A, ROW()), A8, $D$4:INDEX($D:$D, ROW()), D8, $F$4:INDEX($F:$F, ROW()), F8)&gt;1), IFERROR(VALUE(F8), F8), 0)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="54" t="s">
-        <v>295</v>
+      <c r="L8" s="51" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="7" t="s">
-        <v>291</v>
+        <v>326</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>292</v>
+        <v>327</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>296</v>
+        <v>331</v>
       </c>
       <c r="D9" s="13" t="str">
         <f t="shared" si="0"/>
@@ -9307,7 +9628,7 @@
         <v>28000</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>297</v>
+        <v>332</v>
       </c>
       <c r="H9" s="11">
         <v>46117</v>
@@ -9324,19 +9645,19 @@
         <f>IF(AND(J9="FLAG: DUPLICATE INVOICE", COUNTIFS($A$4:INDEX($A:$A, ROW()), A9, $D$4:INDEX($D:$D, ROW()), D9, $F$4:INDEX($F:$F, ROW()), F9)&gt;1), IFERROR(VALUE(F9), F9), 0)</f>
         <v>28000</v>
       </c>
-      <c r="L9" s="54" t="s">
-        <v>298</v>
+      <c r="L9" s="51" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="7" t="s">
-        <v>275</v>
+        <v>310</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>276</v>
+        <v>311</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>299</v>
+        <v>334</v>
       </c>
       <c r="D10" s="13" t="str">
         <f t="shared" si="0"/>
@@ -9349,7 +9670,7 @@
         <v>12850</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>300</v>
+        <v>335</v>
       </c>
       <c r="H10" s="11">
         <v>46114</v>
@@ -9366,19 +9687,19 @@
         <f>IF(AND(J10="FLAG: DUPLICATE INVOICE", COUNTIFS($A$4:INDEX($A:$A, ROW()), A10, $D$4:INDEX($D:$D, ROW()), D10, $F$4:INDEX($F:$F, ROW()), F10)&gt;1), IFERROR(VALUE(F10), F10), 0)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="54" t="s">
-        <v>301</v>
+      <c r="L10" s="51" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="7" t="s">
-        <v>302</v>
+        <v>337</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>303</v>
+        <v>338</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>304</v>
+        <v>339</v>
       </c>
       <c r="D11" s="13" t="str">
         <f t="shared" si="0"/>
@@ -9391,7 +9712,7 @@
         <v>6500</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>305</v>
+        <v>340</v>
       </c>
       <c r="H11" s="11">
         <v>46096</v>
@@ -9408,19 +9729,19 @@
         <f>IF(AND(J11="FLAG: DUPLICATE INVOICE", COUNTIFS($A$4:INDEX($A:$A, ROW()), A11, $D$4:INDEX($D:$D, ROW()), D11, $F$4:INDEX($F:$F, ROW()), F11)&gt;1), IFERROR(VALUE(F11), F11), 0)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="54" t="s">
-        <v>306</v>
+      <c r="L11" s="51" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="7" t="s">
-        <v>302</v>
+        <v>337</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>303</v>
+        <v>338</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>307</v>
+        <v>342</v>
       </c>
       <c r="D12" s="13" t="str">
         <f t="shared" si="0"/>
@@ -9433,7 +9754,7 @@
         <v>6500</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>308</v>
+        <v>343</v>
       </c>
       <c r="H12" s="11">
         <v>46111</v>
@@ -9451,18 +9772,18 @@
         <v>0</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>309</v>
+        <v>344</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="7" t="s">
-        <v>310</v>
+        <v>345</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>311</v>
+        <v>346</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>277</v>
+        <v>312</v>
       </c>
       <c r="D13" s="13" t="str">
         <f t="shared" si="0"/>
@@ -9475,7 +9796,7 @@
         <v>12850</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>312</v>
+        <v>347</v>
       </c>
       <c r="H13" s="11">
         <v>46101</v>
@@ -9493,18 +9814,18 @@
         <v>0</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>313</v>
+        <v>348</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="7" t="s">
-        <v>283</v>
+        <v>318</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>284</v>
+        <v>319</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>314</v>
+        <v>349</v>
       </c>
       <c r="D14" s="13" t="str">
         <f t="shared" si="0"/>
@@ -9517,7 +9838,7 @@
         <v>4750</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>315</v>
+        <v>350</v>
       </c>
       <c r="H14" s="11">
         <v>46113</v>
@@ -9535,74 +9856,74 @@
         <v>0</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>316</v>
+        <v>351</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="30" t="s">
-        <v>317</v>
-      </c>
-      <c r="B15" s="32" t="s">
-        <v>318</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>319</v>
-      </c>
-      <c r="D15" s="34" t="str">
+      <c r="A15" s="28" t="s">
+        <v>352</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>353</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>354</v>
+      </c>
+      <c r="D15" s="32" t="str">
         <f t="shared" si="0"/>
         <v>sec5501</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="29">
         <v>46091</v>
       </c>
-      <c r="F15" s="33">
+      <c r="F15" s="31">
         <v>15200</v>
       </c>
-      <c r="G15" s="32" t="s">
-        <v>320</v>
-      </c>
-      <c r="H15" s="31">
+      <c r="G15" s="30" t="s">
+        <v>355</v>
+      </c>
+      <c r="H15" s="29">
         <v>46105</v>
       </c>
-      <c r="I15" s="34">
+      <c r="I15" s="32">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J15" s="36" t="str">
+      <c r="J15" s="34" t="str">
         <f t="shared" si="2"/>
         <v>OK</v>
       </c>
-      <c r="K15" s="37">
+      <c r="K15" s="35">
         <f>IF(AND(J15="FLAG: DUPLICATE INVOICE", COUNTIFS($A$4:INDEX($A:$A, ROW()), A15, $D$4:INDEX($D:$D, ROW()), D15, $F$4:INDEX($F:$F, ROW()), F15)&gt;1), IFERROR(VALUE(F15), F15), 0)</f>
         <v>0</v>
       </c>
-      <c r="L15" s="32" t="s">
-        <v>321</v>
+      <c r="L15" s="30" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="32" t="s">
-        <v>221</v>
-      </c>
-      <c r="F16" s="33">
+      <c r="A16" s="28" t="s">
+        <v>255</v>
+      </c>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="F16" s="31">
         <f>SUBTOTAL(109,Table_Duplicate_Invoices[Invoice_Amount])</f>
         <v>149850</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="36"/>
-      <c r="K16" s="37">
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="35">
         <f>SUBTOTAL(109,Table_Duplicate_Invoices[Cash_Exposure])</f>
         <v>45600</v>
       </c>
-      <c r="L16" s="32">
+      <c r="L16" s="30">
         <f>SUBTOTAL(103,Table_Duplicate_Invoices[Audit_Workpaper_Notes])</f>
         <v>12</v>
       </c>
@@ -9646,94 +9967,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
-        <v>322</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-    </row>
-    <row r="2" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="69" t="s">
-        <v>323</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-    </row>
-    <row r="3" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="C3" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="E3" s="28" t="s">
-        <v>137</v>
-      </c>
-      <c r="F3" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="G3" s="28" t="s">
-        <v>140</v>
-      </c>
-      <c r="H3" s="29" t="s">
-        <v>324</v>
-      </c>
-      <c r="I3" s="29" t="s">
-        <v>325</v>
-      </c>
-      <c r="J3" s="29" t="s">
-        <v>326</v>
-      </c>
-      <c r="K3" s="29" t="s">
-        <v>327</v>
-      </c>
-      <c r="L3" s="29" t="s">
-        <v>151</v>
-      </c>
-      <c r="M3" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="N3" s="28" t="s">
-        <v>153</v>
+      <c r="A1" s="69" t="s">
+        <v>357</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64"/>
+    </row>
+    <row r="2" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="82" t="s">
+        <v>358</v>
+      </c>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="64"/>
+      <c r="N2" s="64"/>
+    </row>
+    <row r="3" spans="1:14" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="B3" s="60" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" s="60" t="s">
+        <v>168</v>
+      </c>
+      <c r="D3" s="60" t="s">
+        <v>170</v>
+      </c>
+      <c r="E3" s="60" t="s">
+        <v>172</v>
+      </c>
+      <c r="F3" s="60" t="s">
+        <v>126</v>
+      </c>
+      <c r="G3" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="H3" s="61" t="s">
+        <v>359</v>
+      </c>
+      <c r="I3" s="61" t="s">
+        <v>360</v>
+      </c>
+      <c r="J3" s="61" t="s">
+        <v>361</v>
+      </c>
+      <c r="K3" s="61" t="s">
+        <v>362</v>
+      </c>
+      <c r="L3" s="61" t="s">
+        <v>186</v>
+      </c>
+      <c r="M3" s="61" t="s">
+        <v>187</v>
+      </c>
+      <c r="N3" s="61" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="7" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>329</v>
+        <v>364</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="D4" s="12">
         <v>0</v>
@@ -9742,7 +10063,7 @@
         <v>87500</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>331</v>
+        <v>366</v>
       </c>
       <c r="G4" s="19">
         <v>46112.989699074067</v>
@@ -9771,19 +10092,19 @@
         <f t="shared" ref="M4:M15" si="5">IF(L4="FLAG: OFF-HOURS ENTRY", MAX(IFERROR(VALUE(D4), 0), IFERROR(VALUE(E4), 0)), 0)</f>
         <v>87500</v>
       </c>
-      <c r="N4" s="54" t="s">
-        <v>332</v>
+      <c r="N4" s="51" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="7" t="s">
-        <v>333</v>
+        <v>368</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>334</v>
+        <v>369</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>335</v>
+        <v>370</v>
       </c>
       <c r="D5" s="12">
         <v>45000</v>
@@ -9792,7 +10113,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>336</v>
+        <v>371</v>
       </c>
       <c r="G5" s="19">
         <v>46110.594004629631</v>
@@ -9821,19 +10142,19 @@
         <f t="shared" si="5"/>
         <v>45000</v>
       </c>
-      <c r="N5" s="54" t="s">
-        <v>337</v>
+      <c r="N5" s="51" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="7" t="s">
-        <v>338</v>
+        <v>373</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>339</v>
+        <v>374</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>340</v>
+        <v>375</v>
       </c>
       <c r="D6" s="12">
         <v>62000</v>
@@ -9842,7 +10163,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>341</v>
+        <v>376</v>
       </c>
       <c r="G6" s="19">
         <v>46107.187673611108</v>
@@ -9871,19 +10192,19 @@
         <f t="shared" si="5"/>
         <v>62000</v>
       </c>
-      <c r="N6" s="54" t="s">
-        <v>342</v>
+      <c r="N6" s="51" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="7" t="s">
-        <v>343</v>
+        <v>378</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>344</v>
+        <v>379</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>345</v>
+        <v>380</v>
       </c>
       <c r="D7" s="12">
         <v>0</v>
@@ -9892,7 +10213,7 @@
         <v>53000</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>331</v>
+        <v>366</v>
       </c>
       <c r="G7" s="19">
         <v>46109.431076388893</v>
@@ -9921,19 +10242,19 @@
         <f t="shared" si="5"/>
         <v>53000</v>
       </c>
-      <c r="N7" s="54" t="s">
-        <v>346</v>
+      <c r="N7" s="51" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="7" t="s">
-        <v>347</v>
+        <v>382</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>348</v>
+        <v>383</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>349</v>
+        <v>384</v>
       </c>
       <c r="D8" s="12">
         <v>35000</v>
@@ -9942,7 +10263,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>336</v>
+        <v>371</v>
       </c>
       <c r="G8" s="19">
         <v>46112.881944444453</v>
@@ -9971,19 +10292,19 @@
         <f t="shared" si="5"/>
         <v>35000</v>
       </c>
-      <c r="N8" s="54" t="s">
-        <v>350</v>
+      <c r="N8" s="51" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="7" t="s">
-        <v>351</v>
+        <v>386</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>352</v>
+        <v>387</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>353</v>
+        <v>388</v>
       </c>
       <c r="D9" s="12">
         <v>124500</v>
@@ -9992,7 +10313,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>354</v>
+        <v>389</v>
       </c>
       <c r="G9" s="19">
         <v>46106.4375</v>
@@ -10021,19 +10342,19 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N9" s="54" t="s">
-        <v>355</v>
+      <c r="N9" s="51" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="7" t="s">
-        <v>356</v>
+        <v>391</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>357</v>
+        <v>392</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>358</v>
+        <v>393</v>
       </c>
       <c r="D10" s="12">
         <v>0</v>
@@ -10042,7 +10363,7 @@
         <v>124500</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>354</v>
+        <v>389</v>
       </c>
       <c r="G10" s="19">
         <v>46106.4375</v>
@@ -10071,19 +10392,19 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N10" s="54" t="s">
-        <v>359</v>
+      <c r="N10" s="51" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="7" t="s">
-        <v>360</v>
+        <v>395</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>361</v>
+        <v>396</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="D11" s="12">
         <v>14200</v>
@@ -10092,7 +10413,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>331</v>
+        <v>366</v>
       </c>
       <c r="G11" s="19">
         <v>46107.597222222219</v>
@@ -10122,18 +10443,18 @@
         <v>0</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="7" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>366</v>
+        <v>401</v>
       </c>
       <c r="D12" s="12">
         <v>0</v>
@@ -10142,7 +10463,7 @@
         <v>14200</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>331</v>
+        <v>366</v>
       </c>
       <c r="G12" s="19">
         <v>46107.597222222219</v>
@@ -10172,18 +10493,18 @@
         <v>0</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>367</v>
+        <v>402</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="7" t="s">
-        <v>368</v>
+        <v>403</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>369</v>
+        <v>404</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>370</v>
+        <v>405</v>
       </c>
       <c r="D13" s="12">
         <v>8950</v>
@@ -10192,7 +10513,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>336</v>
+        <v>371</v>
       </c>
       <c r="G13" s="19">
         <v>46108.697916666657</v>
@@ -10222,18 +10543,18 @@
         <v>0</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>371</v>
+        <v>406</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="7" t="s">
-        <v>372</v>
+        <v>407</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>373</v>
+        <v>408</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>374</v>
+        <v>409</v>
       </c>
       <c r="D14" s="12">
         <v>95000</v>
@@ -10242,7 +10563,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>354</v>
+        <v>389</v>
       </c>
       <c r="G14" s="19">
         <v>46111.46875</v>
@@ -10272,87 +10593,87 @@
         <v>0</v>
       </c>
       <c r="N14" s="8" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="30" t="s">
-        <v>376</v>
-      </c>
-      <c r="B15" s="32" t="s">
-        <v>377</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>378</v>
-      </c>
-      <c r="D15" s="33">
+      <c r="A15" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>412</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>413</v>
+      </c>
+      <c r="D15" s="31">
         <v>0</v>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="31">
         <v>95000</v>
       </c>
-      <c r="F15" s="32" t="s">
-        <v>354</v>
-      </c>
-      <c r="G15" s="39">
+      <c r="F15" s="30" t="s">
+        <v>389</v>
+      </c>
+      <c r="G15" s="37">
         <v>46111.46875</v>
       </c>
-      <c r="H15" s="34" t="str">
+      <c r="H15" s="32" t="str">
         <f t="shared" si="0"/>
         <v>Monday</v>
       </c>
-      <c r="I15" s="34" t="str">
+      <c r="I15" s="32" t="str">
         <f t="shared" si="1"/>
         <v>11:15:00</v>
       </c>
-      <c r="J15" s="34" t="str">
+      <c r="J15" s="32" t="str">
         <f t="shared" si="2"/>
         <v>NO</v>
       </c>
-      <c r="K15" s="34" t="str">
+      <c r="K15" s="32" t="str">
         <f t="shared" si="3"/>
         <v>NO</v>
       </c>
-      <c r="L15" s="36" t="str">
+      <c r="L15" s="34" t="str">
         <f t="shared" si="4"/>
         <v>OK</v>
       </c>
-      <c r="M15" s="37">
+      <c r="M15" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N15" s="32" t="s">
-        <v>379</v>
+      <c r="N15" s="30" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="B16" s="32"/>
-      <c r="C16" s="32" t="s">
-        <v>221</v>
-      </c>
-      <c r="D16" s="33">
+      <c r="A16" s="28" t="s">
+        <v>255</v>
+      </c>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="D16" s="31">
         <f>SUBTOTAL(109,Table_Off_Hours_GL[Debit_Amount])</f>
         <v>384650</v>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="31">
         <f>SUBTOTAL(109,Table_Off_Hours_GL[Credit_Amount])</f>
         <v>374200</v>
       </c>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="34"/>
-      <c r="K16" s="34"/>
-      <c r="L16" s="36"/>
-      <c r="M16" s="37">
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="34"/>
+      <c r="M16" s="35">
         <f>SUBTOTAL(109,Table_Off_Hours_GL[Financial_Exposure])</f>
         <v>282500</v>
       </c>
-      <c r="N16" s="32">
+      <c r="N16" s="30">
         <f>SUBTOTAL(103,Table_Off_Hours_GL[Audit_Workpaper_Notes])</f>
         <v>12</v>
       </c>
@@ -10393,93 +10714,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
-        <v>380</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-    </row>
-    <row r="2" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="69" t="s">
-        <v>381</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-    </row>
-    <row r="3" spans="1:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="28" t="s">
-        <v>382</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="E3" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="F3" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="G3" s="29" t="s">
-        <v>383</v>
-      </c>
-      <c r="H3" s="29" t="s">
-        <v>384</v>
-      </c>
-      <c r="I3" s="29" t="s">
-        <v>385</v>
-      </c>
-      <c r="J3" s="29" t="s">
-        <v>151</v>
-      </c>
-      <c r="K3" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="L3" s="28" t="s">
-        <v>153</v>
+      <c r="A1" s="69" t="s">
+        <v>415</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+    </row>
+    <row r="2" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="82" t="s">
+        <v>416</v>
+      </c>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+    </row>
+    <row r="3" spans="1:12" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="60" t="s">
+        <v>417</v>
+      </c>
+      <c r="B3" s="60" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="60" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="60" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="60" t="s">
+        <v>124</v>
+      </c>
+      <c r="F3" s="60" t="s">
+        <v>126</v>
+      </c>
+      <c r="G3" s="61" t="s">
+        <v>418</v>
+      </c>
+      <c r="H3" s="61" t="s">
+        <v>419</v>
+      </c>
+      <c r="I3" s="61" t="s">
+        <v>420</v>
+      </c>
+      <c r="J3" s="61" t="s">
+        <v>186</v>
+      </c>
+      <c r="K3" s="61" t="s">
+        <v>187</v>
+      </c>
+      <c r="L3" s="61" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="7" t="s">
-        <v>386</v>
+        <v>421</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>387</v>
+        <v>422</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>388</v>
+        <v>423</v>
       </c>
       <c r="D4" s="12">
         <v>25000</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>389</v>
+        <v>424</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>390</v>
+        <v>425</v>
       </c>
       <c r="G4" s="13" t="str">
         <f t="shared" ref="G4:G15" si="0">IF(AND(ISNUMBER(D4), D4&gt;0), IF(MOD(D4, 1000)=0, "YES", "NO"), "NO")</f>
@@ -10501,28 +10822,28 @@
         <f t="shared" ref="K4:K15" si="4">IF(J4="FLAG: SUSPICIOUS ROUND SUM", D4, 0)</f>
         <v>25000</v>
       </c>
-      <c r="L4" s="54" t="s">
-        <v>391</v>
+      <c r="L4" s="51" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="7" t="s">
-        <v>392</v>
+        <v>427</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>393</v>
+        <v>428</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>394</v>
+        <v>429</v>
       </c>
       <c r="D5" s="12">
         <v>17500</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>395</v>
+        <v>430</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>396</v>
+        <v>431</v>
       </c>
       <c r="G5" s="13" t="str">
         <f t="shared" si="0"/>
@@ -10544,28 +10865,28 @@
         <f t="shared" si="4"/>
         <v>17500</v>
       </c>
-      <c r="L5" s="54" t="s">
-        <v>397</v>
+      <c r="L5" s="51" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="7" t="s">
-        <v>398</v>
+        <v>433</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>399</v>
+        <v>434</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>400</v>
+        <v>435</v>
       </c>
       <c r="D6" s="12">
         <v>10000</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>401</v>
+        <v>436</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>402</v>
+        <v>437</v>
       </c>
       <c r="G6" s="13" t="str">
         <f t="shared" si="0"/>
@@ -10587,28 +10908,28 @@
         <f t="shared" si="4"/>
         <v>10000</v>
       </c>
-      <c r="L6" s="54" t="s">
-        <v>403</v>
+      <c r="L6" s="51" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="7" t="s">
-        <v>404</v>
+        <v>439</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>405</v>
+        <v>440</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>406</v>
+        <v>441</v>
       </c>
       <c r="D7" s="12">
         <v>45000</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>407</v>
+        <v>442</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>408</v>
+        <v>443</v>
       </c>
       <c r="G7" s="13" t="str">
         <f t="shared" si="0"/>
@@ -10630,28 +10951,28 @@
         <f t="shared" si="4"/>
         <v>45000</v>
       </c>
-      <c r="L7" s="54" t="s">
-        <v>409</v>
+      <c r="L7" s="51" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="7" t="s">
-        <v>410</v>
+        <v>445</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>411</v>
+        <v>446</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
       <c r="D8" s="12">
         <v>12000</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>413</v>
+        <v>448</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>414</v>
+        <v>449</v>
       </c>
       <c r="G8" s="13" t="str">
         <f t="shared" si="0"/>
@@ -10673,28 +10994,28 @@
         <f t="shared" si="4"/>
         <v>12000</v>
       </c>
-      <c r="L8" s="54" t="s">
-        <v>415</v>
+      <c r="L8" s="51" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="7" t="s">
-        <v>416</v>
+        <v>451</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>417</v>
+        <v>452</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>418</v>
+        <v>453</v>
       </c>
       <c r="D9" s="12">
         <v>25000</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>419</v>
+        <v>454</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>420</v>
+        <v>455</v>
       </c>
       <c r="G9" s="13" t="str">
         <f t="shared" si="0"/>
@@ -10716,28 +11037,28 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L9" s="54" t="s">
-        <v>421</v>
+      <c r="L9" s="51" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="7" t="s">
-        <v>422</v>
+        <v>457</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>423</v>
+        <v>458</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>424</v>
+        <v>459</v>
       </c>
       <c r="D10" s="12">
         <v>10000</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>425</v>
+        <v>460</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>426</v>
+        <v>461</v>
       </c>
       <c r="G10" s="13" t="str">
         <f t="shared" si="0"/>
@@ -10759,28 +11080,28 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L10" s="54" t="s">
-        <v>427</v>
+      <c r="L10" s="51" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="7" t="s">
-        <v>428</v>
+        <v>463</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>429</v>
+        <v>464</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>388</v>
+        <v>423</v>
       </c>
       <c r="D11" s="12">
         <v>38415.75</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>430</v>
+        <v>465</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>431</v>
+        <v>466</v>
       </c>
       <c r="G11" s="13" t="str">
         <f t="shared" si="0"/>
@@ -10803,27 +11124,27 @@
         <v>0</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>432</v>
+        <v>467</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="7" t="s">
-        <v>433</v>
+        <v>468</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>434</v>
+        <v>469</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>394</v>
+        <v>429</v>
       </c>
       <c r="D12" s="12">
         <v>9420.5</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>435</v>
+        <v>470</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>396</v>
+        <v>431</v>
       </c>
       <c r="G12" s="13" t="str">
         <f t="shared" si="0"/>
@@ -10846,27 +11167,27 @@
         <v>0</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>436</v>
+        <v>471</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="7" t="s">
-        <v>437</v>
+        <v>472</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>438</v>
+        <v>473</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>400</v>
+        <v>435</v>
       </c>
       <c r="D13" s="12">
         <v>2500</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>439</v>
+        <v>474</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>440</v>
+        <v>475</v>
       </c>
       <c r="G13" s="13" t="str">
         <f t="shared" si="0"/>
@@ -10889,27 +11210,27 @@
         <v>0</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>441</v>
+        <v>476</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="7" t="s">
-        <v>442</v>
+        <v>477</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>443</v>
+        <v>478</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>388</v>
+        <v>423</v>
       </c>
       <c r="D14" s="12">
         <v>4000</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>444</v>
+        <v>479</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>445</v>
+        <v>480</v>
       </c>
       <c r="G14" s="13" t="str">
         <f t="shared" si="0"/>
@@ -10932,75 +11253,75 @@
         <v>0</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>446</v>
+        <v>481</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="30" t="s">
-        <v>447</v>
-      </c>
-      <c r="B15" s="32" t="s">
-        <v>448</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>449</v>
-      </c>
-      <c r="D15" s="33">
+      <c r="A15" s="28" t="s">
+        <v>482</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>483</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>484</v>
+      </c>
+      <c r="D15" s="31">
         <v>15000</v>
       </c>
-      <c r="E15" s="32" t="s">
-        <v>450</v>
-      </c>
-      <c r="F15" s="32" t="s">
-        <v>451</v>
-      </c>
-      <c r="G15" s="34" t="str">
+      <c r="E15" s="30" t="s">
+        <v>485</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>486</v>
+      </c>
+      <c r="G15" s="32" t="str">
         <f t="shared" si="0"/>
         <v>YES</v>
       </c>
-      <c r="H15" s="34" t="str">
+      <c r="H15" s="32" t="str">
         <f t="shared" si="1"/>
         <v>YES</v>
       </c>
-      <c r="I15" s="34" t="str">
+      <c r="I15" s="32" t="str">
         <f t="shared" si="2"/>
         <v>NO</v>
       </c>
-      <c r="J15" s="36" t="str">
+      <c r="J15" s="34" t="str">
         <f t="shared" si="3"/>
         <v>OK</v>
       </c>
-      <c r="K15" s="37">
+      <c r="K15" s="35">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L15" s="32" t="s">
-        <v>452</v>
+      <c r="L15" s="30" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="B16" s="32"/>
-      <c r="C16" s="32" t="s">
-        <v>221</v>
-      </c>
-      <c r="D16" s="33">
+      <c r="A16" s="28" t="s">
+        <v>255</v>
+      </c>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="D16" s="31">
         <f>SUBTOTAL(109,Table_Round_Sum_Services[Invoice_Amount])</f>
         <v>213836.25</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="36"/>
-      <c r="K16" s="37">
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="35">
         <f>SUBTOTAL(109,Table_Round_Sum_Services[Financial_Exposure])</f>
         <v>109500</v>
       </c>
-      <c r="L16" s="32">
+      <c r="L16" s="30">
         <f>SUBTOTAL(103,Table_Round_Sum_Services[Audit_Workpaper_Notes])</f>
         <v>12</v>
       </c>
@@ -11038,185 +11359,185 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="57" t="s">
-        <v>453</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
+      <c r="A1" s="69" t="s">
+        <v>488</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="55" t="s">
-        <v>454</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-    </row>
-    <row r="3" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="67" t="s">
-        <v>455</v>
-      </c>
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
+      <c r="A2" s="67" t="s">
+        <v>489</v>
+      </c>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+    </row>
+    <row r="3" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="84" t="s">
+        <v>490</v>
+      </c>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
     </row>
     <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="20" t="s">
-        <v>456</v>
+        <v>491</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>457</v>
+        <v>492</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>458</v>
+        <v>493</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="20" t="s">
-        <v>460</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>461</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>462</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>463</v>
+        <v>494</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="52" t="s">
+        <v>495</v>
+      </c>
+      <c r="B5" s="62" t="s">
+        <v>496</v>
+      </c>
+      <c r="D5" s="52" t="s">
+        <v>497</v>
+      </c>
+      <c r="E5" s="62" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="40" t="s">
-        <v>464</v>
-      </c>
-      <c r="B6" s="42" t="s">
-        <v>465</v>
-      </c>
-      <c r="D6" s="40" t="s">
-        <v>466</v>
-      </c>
-      <c r="E6" s="41" t="s">
+      <c r="A6" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="41" t="s">
+      <c r="D6" s="38" t="s">
         <v>4</v>
       </c>
+      <c r="E6" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="39" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="7" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="72" t="s">
-        <v>467</v>
-      </c>
-      <c r="B7" s="56"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56"/>
+      <c r="A7" s="84" t="s">
+        <v>499</v>
+      </c>
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="71" t="s">
-        <v>468</v>
-      </c>
-      <c r="B8" s="61"/>
-      <c r="C8" s="71" t="s">
-        <v>469</v>
-      </c>
-      <c r="D8" s="61"/>
-      <c r="E8" s="71" t="s">
-        <v>470</v>
-      </c>
-      <c r="F8" s="61"/>
-      <c r="G8" s="71" t="s">
-        <v>471</v>
-      </c>
-      <c r="H8" s="61"/>
+      <c r="A8" s="83" t="s">
+        <v>500</v>
+      </c>
+      <c r="B8" s="72"/>
+      <c r="C8" s="83" t="s">
+        <v>501</v>
+      </c>
+      <c r="D8" s="72"/>
+      <c r="E8" s="83" t="s">
+        <v>502</v>
+      </c>
+      <c r="F8" s="72"/>
+      <c r="G8" s="83" t="s">
+        <v>503</v>
+      </c>
+      <c r="H8" s="72"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="74">
+      <c r="A9" s="85">
         <f>D18</f>
         <v>61</v>
       </c>
-      <c r="B9" s="61"/>
-      <c r="C9" s="74">
+      <c r="B9" s="72"/>
+      <c r="C9" s="85">
         <f>E18</f>
         <v>27</v>
       </c>
-      <c r="D9" s="61"/>
-      <c r="E9" s="75">
+      <c r="D9" s="72"/>
+      <c r="E9" s="87">
         <f>F18</f>
         <v>0.44262295081967212</v>
       </c>
-      <c r="F9" s="61"/>
-      <c r="G9" s="78">
+      <c r="F9" s="72"/>
+      <c r="G9" s="89">
         <f>G18</f>
         <v>823900</v>
       </c>
-      <c r="H9" s="61"/>
+      <c r="H9" s="72"/>
     </row>
     <row r="11" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="67" t="s">
-        <v>472</v>
-      </c>
-      <c r="B11" s="56"/>
-      <c r="C11" s="56"/>
-      <c r="D11" s="56"/>
-      <c r="E11" s="56"/>
-      <c r="F11" s="56"/>
-      <c r="G11" s="56"/>
-      <c r="H11" s="56"/>
+      <c r="A11" s="79" t="s">
+        <v>504</v>
+      </c>
+      <c r="B11" s="64"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
     </row>
     <row r="12" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>473</v>
+        <v>505</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>474</v>
+        <v>506</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>475</v>
+        <v>507</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>476</v>
+        <v>508</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>477</v>
+        <v>509</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>478</v>
+        <v>510</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>479</v>
+        <v>511</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>480</v>
+        <v>512</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>481</v>
+        <v>513</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>482</v>
+        <v>514</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>483</v>
+        <v>515</v>
       </c>
       <c r="D13" s="22">
         <f>COUNTA(Table_Split_POs[PO_Number])</f>
@@ -11235,18 +11556,18 @@
         <v>46600</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>484</v>
+        <v>516</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>485</v>
+        <v>517</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>486</v>
+        <v>518</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>487</v>
+        <v>519</v>
       </c>
       <c r="D14" s="22">
         <f>COUNTA(Table_Dormant_Vendors[Vendor_ID])</f>
@@ -11265,18 +11586,18 @@
         <v>339700</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>488</v>
+        <v>520</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>489</v>
+        <v>521</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>490</v>
+        <v>522</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>491</v>
+        <v>523</v>
       </c>
       <c r="D15" s="22">
         <f>COUNTA(Table_Duplicate_Invoices[Vendor_ID])</f>
@@ -11295,18 +11616,18 @@
         <v>45600</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>492</v>
+        <v>524</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="15" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>494</v>
+        <v>526</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>495</v>
+        <v>527</v>
       </c>
       <c r="D16" s="22">
         <f>COUNTA(Table_Off_Hours_GL[Journal_ID])</f>
@@ -11325,18 +11646,18 @@
         <v>282500</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>496</v>
+        <v>528</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="15" t="s">
-        <v>497</v>
+        <v>529</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>498</v>
+        <v>530</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>499</v>
+        <v>531</v>
       </c>
       <c r="D17" s="22">
         <f>COUNTA(Table_Round_Sum_Services[Invoice_ID])</f>
@@ -11355,14 +11676,14 @@
         <v>109500</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>500</v>
+        <v>532</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="17"/>
       <c r="B18" s="17"/>
       <c r="C18" s="18" t="s">
-        <v>501</v>
+        <v>533</v>
       </c>
       <c r="D18" s="25">
         <f>SUM(D13:D17)</f>
@@ -11383,96 +11704,96 @@
       <c r="H18" s="17"/>
     </row>
     <row r="20" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="72" t="s">
-        <v>502</v>
-      </c>
-      <c r="B20" s="56"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="56"/>
-      <c r="F20" s="56"/>
-      <c r="G20" s="56"/>
-      <c r="H20" s="56"/>
+      <c r="A20" s="84" t="s">
+        <v>534</v>
+      </c>
+      <c r="B20" s="64"/>
+      <c r="C20" s="64"/>
+      <c r="D20" s="64"/>
+      <c r="E20" s="64"/>
+      <c r="F20" s="64"/>
+      <c r="G20" s="64"/>
+      <c r="H20" s="64"/>
     </row>
     <row r="21" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="77" t="s">
-        <v>503</v>
-      </c>
-      <c r="B21" s="56"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="56"/>
+      <c r="A21" s="88" t="s">
+        <v>535</v>
+      </c>
+      <c r="B21" s="64"/>
+      <c r="C21" s="64"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="64"/>
+      <c r="F21" s="64"/>
+      <c r="G21" s="64"/>
+      <c r="H21" s="64"/>
     </row>
     <row r="22" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="73" t="s">
-        <v>504</v>
-      </c>
-      <c r="B22" s="56"/>
-      <c r="C22" s="56"/>
-      <c r="D22" s="56"/>
-      <c r="E22" s="56"/>
-      <c r="F22" s="56"/>
-      <c r="G22" s="56"/>
-      <c r="H22" s="56"/>
+      <c r="A22" s="63" t="s">
+        <v>536</v>
+      </c>
+      <c r="B22" s="64"/>
+      <c r="C22" s="64"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="64"/>
+      <c r="F22" s="64"/>
+      <c r="G22" s="64"/>
+      <c r="H22" s="64"/>
     </row>
     <row r="23" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="76" t="s">
-        <v>505</v>
-      </c>
-      <c r="B23" s="56"/>
-      <c r="C23" s="56"/>
-      <c r="D23" s="56"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="56"/>
-      <c r="G23" s="56"/>
-      <c r="H23" s="56"/>
+      <c r="A23" s="86" t="s">
+        <v>537</v>
+      </c>
+      <c r="B23" s="64"/>
+      <c r="C23" s="64"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="64"/>
+      <c r="F23" s="64"/>
+      <c r="G23" s="64"/>
+      <c r="H23" s="64"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="45" t="s">
-        <v>506</v>
+      <c r="A24" s="53" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="73" t="s">
-        <v>507</v>
-      </c>
-      <c r="B25" s="56"/>
-      <c r="C25" s="56"/>
-      <c r="D25" s="56"/>
-      <c r="E25" s="56"/>
-      <c r="F25" s="56"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="56"/>
+      <c r="A25" s="63" t="s">
+        <v>539</v>
+      </c>
+      <c r="B25" s="64"/>
+      <c r="C25" s="64"/>
+      <c r="D25" s="64"/>
+      <c r="E25" s="64"/>
+      <c r="F25" s="64"/>
+      <c r="G25" s="64"/>
+      <c r="H25" s="64"/>
     </row>
     <row r="26" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="76"/>
-      <c r="B26" s="56"/>
-      <c r="C26" s="56"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="56"/>
-      <c r="H26" s="56"/>
+      <c r="A26" s="86"/>
+      <c r="B26" s="64"/>
+      <c r="C26" s="64"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="64"/>
+      <c r="F26" s="64"/>
+      <c r="G26" s="64"/>
+      <c r="H26" s="64"/>
     </row>
     <row r="27" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="76"/>
-      <c r="B27" s="56"/>
-      <c r="C27" s="56"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="56"/>
-      <c r="F27" s="56"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="56"/>
+      <c r="A27" s="86"/>
+      <c r="B27" s="64"/>
+      <c r="C27" s="64"/>
+      <c r="D27" s="64"/>
+      <c r="E27" s="64"/>
+      <c r="F27" s="64"/>
+      <c r="G27" s="64"/>
+      <c r="H27" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="A25:H25"/>
     <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A27:H27"/>
     <mergeCell ref="E9:F9"/>
-    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A21:H21"/>
     <mergeCell ref="A26:H26"/>
